--- a/source-data/Enerium_Способности_элементов.xlsx
+++ b/source-data/Enerium_Способности_элементов.xlsx
@@ -207,7 +207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7c3008502d841842 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">1d4df3513ce31d02 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="K3" s="3"/>
       <c r="L3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="3"/>
       <c r="L4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="K44" s="3"/>
       <c r="L44">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="K84" s="3"/>
       <c r="L84">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
       <c r="L93">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
       <c r="L101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="K244" s="3"/>
       <c r="L244">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="K245" s="3"/>
       <c r="L245">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
       <c r="L259">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
       <c r="L263">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">e</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -45190,7 +45190,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вычеркнутая ночь (Истечение); Удар заранее (Обрыв нити)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -45730,7 +45730,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">e</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -45745,7 +45745,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каменный молот (Гнев недр); Затянутый узел (Удар маятника)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -46285,7 +46285,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">e</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -46300,7 +46300,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обсидиановые зубья (Гнев недр); Стрела, что находит цель (Кровавый смерч)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -46840,7 +46840,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">e</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -46855,7 +46855,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Укус отставшего (Порезы); Туда, где слабее (Погребальный костёр)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -47395,7 +47395,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">e</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -47410,7 +47410,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Горсть искр (Искра); Низкий полёт (Огненный вал)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -47950,7 +47950,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">e</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -47965,7 +47965,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Три укола (Гнев недр); Снова у входа (Застывание)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -48505,7 +48505,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">e</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -48520,7 +48520,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Три пасти (Искра); Смена маски (Пыльный вихрь)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -49060,7 +49060,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">e</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -49075,7 +49075,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Серп на длинной рукояти (Погребальный костёр); Пелена (Удар маятника)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -49615,7 +49615,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">e</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -49630,7 +49630,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удар из тени (Кровавый смерч); Тень камня (Удар маятника)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>

--- a/source-data/Enerium_Способности_элементов.xlsx
+++ b/source-data/Enerium_Способности_элементов.xlsx
@@ -195,7 +195,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-02 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-06 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -207,7 +207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4c35c2b16b230a2d — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">278287cae2578fab — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 60 %.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H2">
@@ -580,7 +580,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 100 %; перескакивает с врага на врага; горящим +15 %.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 100 % атаки; +15 % по целям под горением (урон каждый ход).</t>
         </is>
       </c>
       <c r="H3">
@@ -591,7 +591,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">перескакивает с врага на врага; горящим +15 %</t>
+          <t xml:space="preserve">+15 % по целям под горением (урон каждый ход)</t>
         </is>
       </c>
       <c r="K3" s="3"/>
@@ -656,7 +656,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 300 %; +25 % за каждый стак горения на цели.</t>
+          <t xml:space="preserve">Мощный удар по цели — 300 % атаки; +25 % за каждый стак горения (урон каждый ход) на цели.</t>
         </is>
       </c>
       <c r="H4">
@@ -667,7 +667,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+25 % за каждый стак горения на цели</t>
+          <t xml:space="preserve">+25 % за каждый стак горения (урон каждый ход) на цели</t>
         </is>
       </c>
       <c r="K4" s="3"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит всех своих — по 60 %.</t>
+          <t xml:space="preserve">Лечит всех своих — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H5">
@@ -787,7 +787,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит троих самых раненых — по 100 %; с теплом +15 %.</t>
+          <t xml:space="preserve">Лечит троих самых раненых — по 100 % атаки; +15 % целям с теплом (лечение каждый ход).</t>
         </is>
       </c>
       <c r="H6">
@@ -798,7 +798,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">с теплом +15 %</t>
+          <t xml:space="preserve">+15 % целям с теплом (лечение каждый ход)</t>
         </is>
       </c>
       <c r="K6" s="3"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сильно лечит самого раненого — 300 %; снимает с цели кровотечение.</t>
+          <t xml:space="preserve">Сильно лечит самого раненого — 300 % атаки; снимает с цели кровотечение (урон каждый ход).</t>
         </is>
       </c>
       <c r="H7">
@@ -857,7 +857,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">снимает с цели кровотечение</t>
+          <t xml:space="preserve">снимает с цели кровотечение (урон каждый ход)</t>
         </is>
       </c>
       <c r="K7" s="3"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит всем своим — по 50 %.</t>
+          <t xml:space="preserve">Щит всем своим — по 50 % атаки.</t>
         </is>
       </c>
       <c r="H8">
@@ -960,7 +960,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит троим самым раненым — по 80 %.</t>
+          <t xml:space="preserve">Щит троим самым раненым — по 80 % атаки.</t>
         </is>
       </c>
       <c r="H9">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит самому раненому — 200 %; кто бьёт по щиту, загорается.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 200 % атаки; кто бьёт по щиту, получает горение: урон 40 % атаки каждый ход, 3 раунда.</t>
         </is>
       </c>
       <c r="H10">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">кто бьёт по щиту, загорается</t>
+          <t xml:space="preserve">кто бьёт по щиту, получает горение: урон 40 % атаки каждый ход, 3 раунда</t>
         </is>
       </c>
       <c r="K10" s="3"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Горение на всех врагов: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Горение на всех врагов, 2 раунда: урон 20 % атаки каждый ход.</t>
         </is>
       </c>
       <c r="H11">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Горение на трёх врагов: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Горение на трёх врагов, 3 раунда: урон 30 % атаки каждый ход, до 2 стаков.</t>
         </is>
       </c>
       <c r="H12">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Горение на цель: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Горение на цель, 3 раунда: урон 40 % атаки каждый ход, до 3 стаков.</t>
         </is>
       </c>
       <c r="H13">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тепло на всех своих: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Тепло на всех своих, 2 раунда: лечение 20 % атаки каждый ход; снимает стужу (замедление).</t>
         </is>
       </c>
       <c r="H14">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тепло на троих самых раненых: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Тепло на троих самых раненых, 3 раунда: лечение 30 % атаки каждый ход, до 2 стаков; снимает стужу (замедление).</t>
         </is>
       </c>
       <c r="H15">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тепло на самого раненого: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Тепло на самого раненого, 3 раунда: лечение 40 % атаки каждый ход, до 3 стаков; снимает стужу (замедление).</t>
         </is>
       </c>
       <c r="H16">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запрет способностей на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Запрет способностей на всех врагов, 1 раунд: цель бьёт только обычной атакой.</t>
         </is>
       </c>
       <c r="H17">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запрет способностей на двух самых опасных врагов, 2 раунда.</t>
+          <t xml:space="preserve">Запрет способностей на двух самых опасных врагов, 2 раунда: цель бьёт только обычной атакой.</t>
         </is>
       </c>
       <c r="H18">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запрет способностей на самого опасного врага, 3 раунда.</t>
+          <t xml:space="preserve">Запрет способностей на самого опасного врага, 3 раунда: цель бьёт только обычной атакой.</t>
         </is>
       </c>
       <c r="H19">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метка на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Метка на всех врагов, 2 раунда: +20 % получаемого урона.</t>
         </is>
       </c>
       <c r="H20">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метка на двух врагов, 3 раунда.</t>
+          <t xml:space="preserve">Метка на двух врагов, 3 раунда: +20 % получаемого урона.</t>
         </is>
       </c>
       <c r="H21">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метка на цель, 4 раунда.</t>
+          <t xml:space="preserve">Метка на цель, 4 раунда: +20 % получаемого урона.</t>
         </is>
       </c>
       <c r="H22">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жар всему отряду, 2 раунда.</t>
+          <t xml:space="preserve">Жар всему отряду, 2 раунда: +20 % наносимого урона.</t>
         </is>
       </c>
       <c r="H23">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жар двум самым сильным союзникам, 3 раунда.</t>
+          <t xml:space="preserve">Жар двум самым сильным союзникам, 3 раунда: +20 % наносимого урона.</t>
         </is>
       </c>
       <c r="H24">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жар самому сильному союзнику, 4 раунда.</t>
+          <t xml:space="preserve">Жар самому сильному союзнику, 4 раунда: +20 % наносимого урона.</t>
         </is>
       </c>
       <c r="H25">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупный урон по цели — 600 %; если цель горит, горение вспыхивает заново с двойной силой.</t>
+          <t xml:space="preserve">Крупный урон по цели — 600 % атаки; если на цели есть горение (урон каждый ход), оно вспыхивает заново — вдвое сильнее.</t>
         </is>
       </c>
       <c r="H26">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">если цель горит, горение вспыхивает заново с двойной силой</t>
+          <t xml:space="preserve">если на цели есть горение (урон каждый ход), оно вспыхивает заново — вдвое сильнее</t>
         </is>
       </c>
       <c r="K26" s="3"/>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупное лечение всего отряда — по 120 %.</t>
+          <t xml:space="preserve">Крупное лечение всего отряда — по 120 % атаки.</t>
         </is>
       </c>
       <c r="H27">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит всему отряду — по 100 %; кто бьёт по щиту, загорается.</t>
+          <t xml:space="preserve">Крепкий щит всему отряду — по 100 % атаки; кто бьёт по щиту, получает горение: урон 40 % атаки каждый ход, 3 раунда.</t>
         </is>
       </c>
       <c r="H28">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">кто бьёт по щиту, загорается</t>
+          <t xml:space="preserve">кто бьёт по щиту, получает горение: урон 40 % атаки каждый ход, 3 раунда</t>
         </is>
       </c>
       <c r="K28" s="3"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Горение на всех врагов: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Горение на всех врагов, 3 раунда: урон каждый ход — сразу 3 стака по 40 % атаки.</t>
         </is>
       </c>
       <c r="H29">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тепло на весь отряд: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Тепло на весь отряд, 3 раунда: лечение каждый ход — сразу 3 стака по 40 % атаки; снимает стужу (замедление).</t>
         </is>
       </c>
       <c r="H30">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запрет способностей на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Запрет способностей на всех врагов, 2 раунда: цель бьёт только обычной атакой.</t>
         </is>
       </c>
       <c r="H31">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метка на всех врагов: +30 % получаемого урона, 4 раунда.</t>
+          <t xml:space="preserve">Метка на всех врагов, 4 раунда: +30 % получаемого урона.</t>
         </is>
       </c>
       <c r="H32">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жар всему отряду: +30 % урона, 4 раунда.</t>
+          <t xml:space="preserve">Жар всему отряду, 4 раунда: +30 % наносимого урона.</t>
         </is>
       </c>
       <c r="H33">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каждая третья обычная атака героя поджигает цель: 1 стак горения.</t>
+          <t xml:space="preserve">Каждая третья обычная атака героя кладёт на цель горение: урон 40 % атаки каждый ход, 3 раунда.</t>
         </is>
       </c>
       <c r="J34" s="3"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % урона, пока горит хотя бы один враг.</t>
+          <t xml:space="preserve">+10 % урона, пока хотя бы на одном враге есть горение (урон каждый ход).</t>
         </is>
       </c>
       <c r="J35" s="3"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Горение героя держится на раунд дольше.</t>
+          <t xml:space="preserve">Горение героя (урон каждый ход) держится на 1 раунд дольше.</t>
         </is>
       </c>
       <c r="J36" s="3"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение и щиты героя на 10 % сильнее, пока горит хотя бы один враг.</t>
+          <t xml:space="preserve">Лечение и щиты героя на 10 % сильнее, пока хотя бы на одном враге есть горение (урон каждый ход).</t>
         </is>
       </c>
       <c r="J37" s="3"/>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каждая третья обычная атака героя кладёт на цель метку на 2 раунда.</t>
+          <t xml:space="preserve">Каждая третья обычная атака героя кладёт на цель метку на 2 раунда: +20 % получаемого урона.</t>
         </is>
       </c>
       <c r="J38" s="3"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 % шанс поджечь атакующего — 1 стак горения.</t>
+          <t xml:space="preserve">Когда героя ударили, есть шанс наложить на атакующего горение: урон 40 % атаки каждый ход, 3 раунда.</t>
         </is>
       </c>
       <c r="H39">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цель получает 1 стак горения.</t>
+          <t xml:space="preserve">Когда герой нанёс крит, цель получает горение: урон 40 % атаки каждый ход, 3 раунда.</t>
         </is>
       </c>
       <c r="J40" s="3"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Если враг горел, горение со всеми стаками переходит на случайного врага.</t>
+          <t xml:space="preserve">Когда герой добил врага, на котором было горение (урон каждый ход), оно со всеми стаками переходит на случайного врага.</t>
         </is>
       </c>
       <c r="J41" s="3"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отряду +15 % урона до конца этажа.</t>
+          <t xml:space="preserve">Когда союзник пал, отряд до конца этажа наносит на 15 % больше урона.</t>
         </is>
       </c>
       <c r="J42" s="3"/>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 60 %.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H43">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 100 %; отравленным +15 %.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 100 % атаки; +15 % по целям под ядом (урон каждый ход).</t>
         </is>
       </c>
       <c r="H44">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">отравленным +15 %</t>
+          <t xml:space="preserve">+15 % по целям под ядом (урон каждый ход)</t>
         </is>
       </c>
       <c r="K44" s="3"/>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 300 %; при 3 стаках яда на цели — ещё паралич на раунд.</t>
+          <t xml:space="preserve">Мощный удар по цели — 300 % атаки; если на цели 3 стака яда (урон каждый ход) — ещё паралич (без обычных атак) на 1 раунд.</t>
         </is>
       </c>
       <c r="H45">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">при 3 стаках яда на цели — ещё паралич на раунд</t>
+          <t xml:space="preserve">если на цели 3 стака яда (урон каждый ход) — ещё паралич (без обычных атак) на 1 раунд</t>
         </is>
       </c>
       <c r="K45" s="3"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит всех своих — по 60 %.</t>
+          <t xml:space="preserve">Лечит всех своих — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H46">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит троих самых раненых — по 100 %; с живицей +15 %.</t>
+          <t xml:space="preserve">Лечит троих самых раненых — по 100 % атаки; +15 % целям с живицей (лечение каждый ход).</t>
         </is>
       </c>
       <c r="H47">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">с живицей +15 %</t>
+          <t xml:space="preserve">+15 % целям с живицей (лечение каждый ход)</t>
         </is>
       </c>
       <c r="K47" s="3"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сильно лечит самого раненого — 300 %; с живицей +25 %.</t>
+          <t xml:space="preserve">Сильно лечит самого раненого — 300 % атаки; +25 % цели с живицей (лечение каждый ход).</t>
         </is>
       </c>
       <c r="H48">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">с живицей +25 %</t>
+          <t xml:space="preserve">+25 % цели с живицей (лечение каждый ход)</t>
         </is>
       </c>
       <c r="K48" s="3"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит всем своим — по 50 %.</t>
+          <t xml:space="preserve">Щит всем своим — по 50 % атаки.</t>
         </is>
       </c>
       <c r="H49">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит троим самым раненым — по 80 %.</t>
+          <t xml:space="preserve">Щит троим самым раненым — по 80 % атаки.</t>
         </is>
       </c>
       <c r="H50">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит самому раненому — 200 %.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 200 % атаки.</t>
         </is>
       </c>
       <c r="H51">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Яд на всех врагов: 15 % за ход, 3 раунда.</t>
+          <t xml:space="preserve">Яд на всех врагов, 3 раунда: урон 15 % атаки каждый ход.</t>
         </is>
       </c>
       <c r="H52">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Яд на трёх врагов: 25 % за ход, 4 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Яд на трёх врагов, 4 раунда: урон 25 % атаки каждый ход, до 2 стаков.</t>
         </is>
       </c>
       <c r="H53">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Яд на цель: 35 % за ход, 4 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Яд на цель, 4 раунда: урон 35 % атаки каждый ход, до 3 стаков.</t>
         </is>
       </c>
       <c r="H54">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Живица на всех своих: 15 % за ход, 3 раунда.</t>
+          <t xml:space="preserve">Живица на всех своих, 3 раунда: лечение 15 % атаки каждый ход.</t>
         </is>
       </c>
       <c r="H55">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Живица на троих самых раненых: 25 % за ход, 4 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Живица на троих самых раненых, 4 раунда: лечение 25 % атаки каждый ход, до 2 стаков.</t>
         </is>
       </c>
       <c r="H56">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Живица на самого раненого: 35 % за ход, 4 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Живица на самого раненого, 4 раунда: лечение 35 % атаки каждый ход, до 3 стаков.</t>
         </is>
       </c>
       <c r="H57">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Паралич на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Паралич на всех врагов, 1 раунд: цель без обычной атаки — ходит только способностью.</t>
         </is>
       </c>
       <c r="H58">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Паралич на двух самых опасных врагов, 2 раунда.</t>
+          <t xml:space="preserve">Паралич на двух самых опасных врагов, 2 раунда: цель без обычной атаки — ходит только способностью.</t>
         </is>
       </c>
       <c r="H59">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Паралич на самого опасного врага, 3 раунда.</t>
+          <t xml:space="preserve">Паралич на самого опасного врага, 3 раунда: цель без обычной атаки — ходит только способностью.</t>
         </is>
       </c>
       <c r="H60">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осыпание на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Осыпание на всех врагов, 2 раунда: −30 % физической защиты.</t>
         </is>
       </c>
       <c r="H61">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осыпание на двух врагов, 3 раунда.</t>
+          <t xml:space="preserve">Осыпание на двух врагов, 3 раунда: −30 % физической защиты.</t>
         </is>
       </c>
       <c r="H62">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осыпание на цель, 4 раунда.</t>
+          <t xml:space="preserve">Осыпание на цель, 4 раунда: −30 % физической защиты.</t>
         </is>
       </c>
       <c r="H63">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каменная кожа всему отряду, 2 раунда.</t>
+          <t xml:space="preserve">Каменная кожа всему отряду, 2 раунда: −25 % получаемого урона.</t>
         </is>
       </c>
       <c r="H64">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каменная кожа двум самым раненым союзникам, 3 раунда.</t>
+          <t xml:space="preserve">Каменная кожа двум самым раненым союзникам, 3 раунда: −25 % получаемого урона.</t>
         </is>
       </c>
       <c r="H65">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каменная кожа самому раненому союзнику, 4 раунда.</t>
+          <t xml:space="preserve">Каменная кожа самому раненому союзнику, 4 раунда: −25 % получаемого урона.</t>
         </is>
       </c>
       <c r="H66">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупный урон по цели — 600 %; и паралич цели на 2 раунда.</t>
+          <t xml:space="preserve">Крупный урон по цели — 600 % атаки; паралич (без обычных атак) на 2 раунда.</t>
         </is>
       </c>
       <c r="H67">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">и паралич цели на 2 раунда</t>
+          <t xml:space="preserve">паралич (без обычных атак) на 2 раунда</t>
         </is>
       </c>
       <c r="K67" s="3"/>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупное лечение всего отряда — по 120 %.</t>
+          <t xml:space="preserve">Крупное лечение всего отряда — по 120 % атаки.</t>
         </is>
       </c>
       <c r="H68">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит всему отряду — по 100 %.</t>
+          <t xml:space="preserve">Крепкий щит всему отряду — по 100 % атаки.</t>
         </is>
       </c>
       <c r="H69">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Яд на всех врагов: сразу 3 стака по 30 %, 4 раунда.</t>
+          <t xml:space="preserve">Яд на всех врагов, 4 раунда: урон каждый ход — сразу 3 стака по 30 % атаки.</t>
         </is>
       </c>
       <c r="H70">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Живица на весь отряд: сразу 3 стака по 30 %, 4 раунда.</t>
+          <t xml:space="preserve">Живица на весь отряд, 4 раунда: лечение каждый ход — сразу 3 стака по 30 % атаки.</t>
         </is>
       </c>
       <c r="H71">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Паралич на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Паралич на всех врагов, 2 раунда: цель без обычной атаки — ходит только способностью.</t>
         </is>
       </c>
       <c r="H72">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осыпание на всех врагов: −45 % физической защиты, 4 раунда.</t>
+          <t xml:space="preserve">Осыпание на всех врагов, 4 раунда: −45 % физической защиты.</t>
         </is>
       </c>
       <c r="H73">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каменная кожа всему отряду: −35 % получаемого урона, 4 раунда.</t>
+          <t xml:space="preserve">Каменная кожа всему отряду, 4 раунда: −35 % получаемого урона.</t>
         </is>
       </c>
       <c r="H74">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">−10 % получаемого физического урона.</t>
+          <t xml:space="preserve">−10 % получаемого физического урона.</t>
         </is>
       </c>
       <c r="J75" s="3"/>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Яд героя держится на раунд дольше.</t>
+          <t xml:space="preserve">Яд героя (урон каждый ход) держится на 1 раунд дольше.</t>
         </is>
       </c>
       <c r="J76" s="3"/>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % урона по целям с осыпанием.</t>
+          <t xml:space="preserve">+10 % урона по целям под осыпанием (меньше физической защиты).</t>
         </is>
       </c>
       <c r="J77" s="3"/>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щиты героя на 15 % крепче.</t>
+          <t xml:space="preserve">Щиты героя на 15 % крепче.</t>
         </is>
       </c>
       <c r="J78" s="3"/>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каждая третья обычная атака героя кладёт на цель осыпание на 2 раунда.</t>
+          <t xml:space="preserve">Каждая третья обычная атака героя кладёт на цель осыпание на 2 раунда: −30 % физической защиты.</t>
         </is>
       </c>
       <c r="J79" s="3"/>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Союзник под живицей героя получает на 10 % меньше урона.</t>
+          <t xml:space="preserve">Союзник под живицей героя (лечение каждый ход) получает на 10 % меньше урона.</t>
         </is>
       </c>
       <c r="J80" s="3"/>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пока герой жив, отряд наносит +10 % урона парализованным целям.</t>
+          <t xml:space="preserve">Пока герой жив, отряд наносит +10 % урона целям под параличом (без обычных атак).</t>
         </is>
       </c>
       <c r="J81" s="3"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 % шанс получить щит на 5 % здоровья.</t>
+          <t xml:space="preserve">Когда героя ударили, есть шанс получить щит на 5 % здоровья.</t>
         </is>
       </c>
       <c r="H82">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Этот крит наносит на 30 % меньше урона.</t>
+          <t xml:space="preserve">Когда по герою прошёл крит, этот крит наносит на 30 % меньше урона.</t>
         </is>
       </c>
       <c r="J83" s="3"/>
@@ -5127,14 +5127,14 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каменная кожа на 2 раунда.</t>
+          <t xml:space="preserve">Когда здоровье героя упало ниже 50 % (раз за этаж), герой получает каменную кожу на 2 раунда: −25 % получаемого урона.</t>
         </is>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">здоровье героя упало ниже половины — раз за этаж</t>
+          <t xml:space="preserve">здоровье героя упало ниже 50 % — раз за этаж</t>
         </is>
       </c>
       <c r="M84">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Все враги получают 1 стак яда.</t>
+          <t xml:space="preserve">Когда герой добил врага, все враги получают яд: урон 15 % атаки каждый ход, 3 раунда.</t>
         </is>
       </c>
       <c r="J85" s="3"/>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 60 %; каждому — стак пореза.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 60 % атаки; каждому — порезы: урон 15 % атаки каждый ход, 1 раунд.</t>
         </is>
       </c>
       <c r="H86">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">каждому — стак пореза</t>
+          <t xml:space="preserve">каждому — порезы: урон 15 % атаки каждый ход, 1 раунд</t>
         </is>
       </c>
       <c r="K86" s="3"/>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 100 %; с порезами +15 %.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 100 % атаки; +15 % по целям с порезами (урон каждый ход).</t>
         </is>
       </c>
       <c r="H87">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">с порезами +15 %</t>
+          <t xml:space="preserve">+15 % по целям с порезами (урон каждый ход)</t>
         </is>
       </c>
       <c r="K87" s="3"/>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 300 %; снимает с цели все порезы, +20 % урона за каждый.</t>
+          <t xml:space="preserve">Мощный удар по цели — 300 % атаки; снимает с цели все порезы (урон каждый ход): +20 % урона за каждый стак.</t>
         </is>
       </c>
       <c r="H88">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">снимает с цели все порезы, +20 % урона за каждый</t>
+          <t xml:space="preserve">снимает с цели все порезы (урон каждый ход): +20 % урона за каждый стак</t>
         </is>
       </c>
       <c r="K88" s="3"/>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит всех своих — по 60 %.</t>
+          <t xml:space="preserve">Лечит всех своих — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H89">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит троих самых раненых — по 100 %; со свежим ветром +15 %.</t>
+          <t xml:space="preserve">Лечит троих самых раненых — по 100 % атаки; +15 % целям со свежим ветром (лечение каждый ход).</t>
         </is>
       </c>
       <c r="H90">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">со свежим ветром +15 %</t>
+          <t xml:space="preserve">+15 % целям со свежим ветром (лечение каждый ход)</t>
         </is>
       </c>
       <c r="K90" s="3"/>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сильно лечит самого раненого — 300 %; со свежим ветром +25 %.</t>
+          <t xml:space="preserve">Сильно лечит самого раненого — 300 % атаки; +25 % цели со свежим ветром (лечение каждый ход).</t>
         </is>
       </c>
       <c r="H91">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">со свежим ветром +25 %</t>
+          <t xml:space="preserve">+25 % цели со свежим ветром (лечение каждый ход)</t>
         </is>
       </c>
       <c r="K91" s="3"/>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит всем своим — по 50 %.</t>
+          <t xml:space="preserve">Щит всем своим — по 50 % атаки.</t>
         </is>
       </c>
       <c r="H92">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит троим самым раненым — по 80 %.</t>
+          <t xml:space="preserve">Щит троим самым раненым — по 80 % атаки.</t>
         </is>
       </c>
       <c r="H93">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит самому раненому — 200 %; пока щит цел, +10 % уклонения.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 200 % атаки; пока щит цел, +10 % уклонения.</t>
         </is>
       </c>
       <c r="H94">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">пока щит цел, +10 % уклонения</t>
+          <t xml:space="preserve">пока щит цел, +10 % уклонения</t>
         </is>
       </c>
       <c r="K94" s="3"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Порезы на всех врагов: 15 % за ход, 1 раунд, до 2 стаков.</t>
+          <t xml:space="preserve">Порезы на всех врагов, 1 раунд: урон 15 % атаки каждый ход, до 2 стаков.</t>
         </is>
       </c>
       <c r="H95">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Порезы на трёх врагов: 25 % за ход, 2 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Порезы на трёх врагов, 2 раунда: урон 25 % атаки каждый ход, до 3 стаков.</t>
         </is>
       </c>
       <c r="H96">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Порезы на цель: 35 % за ход, 2 раунда, до 4 стаков.</t>
+          <t xml:space="preserve">Порезы на цель, 2 раунда: урон 35 % атаки каждый ход, до 4 стаков.</t>
         </is>
       </c>
       <c r="H97">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Свежий ветер на всех своих: 15 % за ход, 1 раунд, до 2 стаков.</t>
+          <t xml:space="preserve">Свежий ветер на всех своих, 1 раунд: лечение 15 % атаки каждый ход, до 2 стаков.</t>
         </is>
       </c>
       <c r="H98">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Свежий ветер на троих самых раненых: 25 % за ход, 2 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Свежий ветер на троих самых раненых, 2 раунда: лечение 25 % атаки каждый ход, до 3 стаков.</t>
         </is>
       </c>
       <c r="H99">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Свежий ветер на самого раненого: 35 % за ход, 2 раунда, до 4 стаков.</t>
+          <t xml:space="preserve">Свежий ветер на самого раненого, 2 раунда: лечение 35 % атаки каждый ход, до 4 стаков.</t>
         </is>
       </c>
       <c r="H100">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сброс на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Сброс на всех врагов, 1 раунд: цель пропускает ход и заново выбирает, кого бить.</t>
         </is>
       </c>
       <c r="H101">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сброс на двух самых опасных врагов, 2 раунда.</t>
+          <t xml:space="preserve">Сброс на двух самых опасных врагов, 2 раунда: цель пропускает ход и заново выбирает, кого бить.</t>
         </is>
       </c>
       <c r="H102">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сброс на самого опасного врага, 3 раунда.</t>
+          <t xml:space="preserve">Сброс на самого опасного врага, 3 раунда: цель пропускает ход и заново выбирает, кого бить.</t>
         </is>
       </c>
       <c r="H103">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слепота на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Слепота на всех врагов, 2 раунда: +50 % к шансу промаха.</t>
         </is>
       </c>
       <c r="H104">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слепота на двух врагов, 3 раунда.</t>
+          <t xml:space="preserve">Слепота на двух врагов, 3 раунда: +50 % к шансу промаха.</t>
         </is>
       </c>
       <c r="H105">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слепота на цель, 4 раунда.</t>
+          <t xml:space="preserve">Слепота на цель, 4 раунда: +50 % к шансу промаха.</t>
         </is>
       </c>
       <c r="H106">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Попутный ветер всему отряду, 2 раунда.</t>
+          <t xml:space="preserve">Попутный ветер всему отряду, 2 раунда: +20 % уклонения.</t>
         </is>
       </c>
       <c r="H107">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Попутный ветер двум самым раненым союзникам, 3 раунда.</t>
+          <t xml:space="preserve">Попутный ветер двум самым раненым союзникам, 3 раунда: +20 % уклонения.</t>
         </is>
       </c>
       <c r="H108">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Попутный ветер самому раненому союзнику, 4 раунда.</t>
+          <t xml:space="preserve">Попутный ветер самому раненому союзнику, 4 раунда: +20 % уклонения.</t>
         </is>
       </c>
       <c r="H109">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пять ударов по цели, по 120 %; каждый накладывает порез.</t>
+          <t xml:space="preserve">Пять ударов по цели — по 120 % атаки; каждый накладывает порезы: урон 35 % атаки каждый ход, 2 раунда, до 4 стаков.</t>
         </is>
       </c>
       <c r="H110">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупное лечение всего отряда — по 120 %.</t>
+          <t xml:space="preserve">Крупное лечение всего отряда — по 120 % атаки.</t>
         </is>
       </c>
       <c r="H111">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит всему отряду — по 100 %.</t>
+          <t xml:space="preserve">Крепкий щит всему отряду — по 100 % атаки.</t>
         </is>
       </c>
       <c r="H112">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Порезы на всех врагов: сразу 3 стака по 30 %, 2 раунда.</t>
+          <t xml:space="preserve">Порезы на всех врагов, 2 раунда: урон каждый ход — сразу 3 стака по 30 % атаки.</t>
         </is>
       </c>
       <c r="H113">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Свежий ветер на весь отряд: сразу 3 стака по 30 %, 2 раунда.</t>
+          <t xml:space="preserve">Свежий ветер на весь отряд, 2 раунда: лечение каждый ход — сразу 3 стака по 30 % атаки.</t>
         </is>
       </c>
       <c r="H114">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сброс на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Сброс на всех врагов, 2 раунда: цель пропускает ход и заново выбирает, кого бить.</t>
         </is>
       </c>
       <c r="H115">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слепота на всех врагов: +75 % промахов, 4 раунда.</t>
+          <t xml:space="preserve">Слепота на всех врагов, 4 раунда: +75 % к шансу промаха.</t>
         </is>
       </c>
       <c r="H116">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Попутный ветер всему отряду: +30 % уклонения, 4 раунда.</t>
+          <t xml:space="preserve">Попутный ветер всему отряду, 4 раунда: +30 % уклонения.</t>
         </is>
       </c>
       <c r="H117">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупный урон по всем врагам — по 120 %; каждому — стак пореза.</t>
+          <t xml:space="preserve">Крупный урон по всем врагам — по 120 % атаки; каждому — порезы: урон 15 % атаки каждый ход, 1 раунд.</t>
         </is>
       </c>
       <c r="H118">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">каждому — стак пореза</t>
+          <t xml:space="preserve">каждому — порезы: урон 15 % атаки каждый ход, 1 раунд</t>
         </is>
       </c>
       <c r="K118" s="3"/>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+8 % уклонения.</t>
+          <t xml:space="preserve">+8 % уклонения.</t>
         </is>
       </c>
       <c r="J119" s="3"/>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % скорости, пока на враге есть порезы.</t>
+          <t xml:space="preserve">+10 % скорости, пока хотя бы на одном враге есть порезы (урон каждый ход).</t>
         </is>
       </c>
       <c r="J120" s="3"/>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % урона по целям под слепотой.</t>
+          <t xml:space="preserve">+10 % урона по целям под слепотой (промахи).</t>
         </is>
       </c>
       <c r="J121" s="3"/>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Порезы героя держатся на раунд дольше.</t>
+          <t xml:space="preserve">Порезы героя (урон каждый ход) держатся на 1 раунд дольше.</t>
         </is>
       </c>
       <c r="J122" s="3"/>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Союзник под свежим ветром героя получает +8 % уклонения.</t>
+          <t xml:space="preserve">Союзник под свежим ветром героя (лечение каждый ход) получает +8 % уклонения.</t>
         </is>
       </c>
       <c r="J123" s="3"/>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Контрудар обычной атакой и порез.</t>
+          <t xml:space="preserve">Когда герой увернулся, он отвечает обычной атакой и накладывает порезы: урон 35 % атаки каждый ход, 2 раунда.</t>
         </is>
       </c>
       <c r="J124" s="3"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+5 % уклонения до конца этажа, всего не больше +20 %.</t>
+          <t xml:space="preserve">Когда героя ударили, он получает +5 % уклонения до конца этажа — всего не больше +20 %.</t>
         </is>
       </c>
       <c r="J125" s="3"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">В следующем раунде герой ходит первым.</t>
+          <t xml:space="preserve">Когда герой нанёс крит, в следующем раунде он ходит первым.</t>
         </is>
       </c>
       <c r="J126" s="3"/>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 % шанс увернуться от этой ульты.</t>
+          <t xml:space="preserve">Когда враг применил ульту, есть шанс увернуться от неё.</t>
         </is>
       </c>
       <c r="H127">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 60 %.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H128">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 100 %; с увяданием +10 %.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 100 % атаки; +10 % по целям под увяданием (урон каждый ход).</t>
         </is>
       </c>
       <c r="H129">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">с увяданием +10 %</t>
+          <t xml:space="preserve">+10 % по целям под увяданием (урон каждый ход)</t>
         </is>
       </c>
       <c r="K129" s="3"/>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 300 %; +20 % по цели ниже 30 % здоровья.</t>
+          <t xml:space="preserve">Мощный удар по цели — 300 % атаки; +20 % по цели ниже 30 % здоровья.</t>
         </is>
       </c>
       <c r="H130">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+20 % по цели ниже 30 % здоровья</t>
+          <t xml:space="preserve">+20 % по цели ниже 30 % здоровья</t>
         </is>
       </c>
       <c r="K130" s="3"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит всех своих — по 60 %.</t>
+          <t xml:space="preserve">Лечит всех своих — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H131">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит троих самых раненых — по 100 %; +15 % по целям ниже половины здоровья.</t>
+          <t xml:space="preserve">Лечит троих самых раненых — по 100 % атаки; +15 % целям ниже 50 % здоровья.</t>
         </is>
       </c>
       <c r="H132">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+15 % по целям ниже половины здоровья</t>
+          <t xml:space="preserve">+15 % целям ниже 50 % здоровья</t>
         </is>
       </c>
       <c r="K132" s="3"/>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сильно лечит самого раненого — 300 %; с тёмной кровью +25 %.</t>
+          <t xml:space="preserve">Сильно лечит самого раненого — 300 % атаки; +25 % цели с тёмной кровью (лечение каждый ход).</t>
         </is>
       </c>
       <c r="H133">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">с тёмной кровью +25 %</t>
+          <t xml:space="preserve">+25 % цели с тёмной кровью (лечение каждый ход)</t>
         </is>
       </c>
       <c r="K133" s="3"/>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит всем своим — по 50 %.</t>
+          <t xml:space="preserve">Щит всем своим — по 50 % атаки.</t>
         </is>
       </c>
       <c r="H134">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит троим самым раненым — по 80 %.</t>
+          <t xml:space="preserve">Щит троим самым раненым — по 80 % атаки.</t>
         </is>
       </c>
       <c r="H135">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит самому раненому — 200 %.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 200 % атаки.</t>
         </is>
       </c>
       <c r="H136">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Увядание на всех врагов: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Увядание на всех врагов, 2 раунда: урон 20 % атаки каждый ход; 10 % урона лечат наложившего.</t>
         </is>
       </c>
       <c r="H137">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Увядание на трёх врагов: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Увядание на трёх врагов, 3 раунда: урон 30 % атаки каждый ход, до 2 стаков; 10 % урона лечат наложившего.</t>
         </is>
       </c>
       <c r="H138">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Увядание на цель: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Увядание на цель, 3 раунда: урон 40 % атаки каждый ход, до 3 стаков; 10 % урона лечат наложившего.</t>
         </is>
       </c>
       <c r="H139">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тёмная кровь на всех своих: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Тёмная кровь на всех своих, 2 раунда: лечение 20 % атаки каждый ход; вдвое сильнее, пока цель ниже 30 % здоровья.</t>
         </is>
       </c>
       <c r="H140">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тёмная кровь на троих самых раненых: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Тёмная кровь на троих самых раненых, 3 раунда: лечение 30 % атаки каждый ход, до 2 стаков; вдвое сильнее, пока цель ниже 30 % здоровья.</t>
         </is>
       </c>
       <c r="H141">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тёмная кровь на самого раненого: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Тёмная кровь на самого раненого, 3 раунда: лечение 40 % атаки каждый ход, до 3 стаков; вдвое сильнее, пока цель ниже 30 % здоровья.</t>
         </is>
       </c>
       <c r="H142">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ужас на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Ужас на всех врагов, 1 раунд: цель не действует, пока не получит удар.</t>
         </is>
       </c>
       <c r="H143">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ужас на двух самых опасных врагов, 2 раунда.</t>
+          <t xml:space="preserve">Ужас на двух самых опасных врагов, 2 раунда: цель не действует, пока не получит удар.</t>
         </is>
       </c>
       <c r="H144">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ужас на самого опасного врага, 3 раунда.</t>
+          <t xml:space="preserve">Ужас на самого опасного врага, 3 раунда: цель не действует, пока не получит удар.</t>
         </is>
       </c>
       <c r="H145">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ослабление на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Ослабление на всех врагов, 2 раунда: −25 % наносимого урона.</t>
         </is>
       </c>
       <c r="H146">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ослабление на двух врагов, 3 раунда.</t>
+          <t xml:space="preserve">Ослабление на двух врагов, 3 раунда: −25 % наносимого урона.</t>
         </is>
       </c>
       <c r="H147">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ослабление на цель, 4 раунда.</t>
+          <t xml:space="preserve">Ослабление на цель, 4 раунда: −25 % наносимого урона.</t>
         </is>
       </c>
       <c r="H148">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кровожадность всему отряду, 2 раунда.</t>
+          <t xml:space="preserve">Кровожадность всему отряду, 2 раунда: удары лечат на 15 % нанесённого урона.</t>
         </is>
       </c>
       <c r="H149">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кровожадность двум самым сильным союзникам, 3 раунда.</t>
+          <t xml:space="preserve">Кровожадность двум самым сильным союзникам, 3 раунда: удары лечат на 15 % нанесённого урона.</t>
         </is>
       </c>
       <c r="H150">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кровожадность самому сильному союзнику, 4 раунда.</t>
+          <t xml:space="preserve">Кровожадность самому сильному союзнику, 4 раунда: удары лечат на 15 % нанесённого урона.</t>
         </is>
       </c>
       <c r="H151">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупный урон по цели — 600 %; герой лечится на четверть нанесённого.</t>
+          <t xml:space="preserve">Крупный урон по цели — 600 % атаки; герой лечится на 25 % нанесённого урона.</t>
         </is>
       </c>
       <c r="H152">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">герой лечится на четверть нанесённого</t>
+          <t xml:space="preserve">герой лечится на 25 % нанесённого урона</t>
         </is>
       </c>
       <c r="K152" s="3"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупное лечение всего отряда — по 120 %.</t>
+          <t xml:space="preserve">Крупное лечение всего отряда — по 120 % атаки.</t>
         </is>
       </c>
       <c r="H153">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит всему отряду — по 100 %.</t>
+          <t xml:space="preserve">Крепкий щит всему отряду — по 100 % атаки.</t>
         </is>
       </c>
       <c r="H154">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Увядание на всех врагов: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Увядание на всех врагов, 3 раунда: урон каждый ход — сразу 3 стака по 40 % атаки; 10 % урона лечат наложившего.</t>
         </is>
       </c>
       <c r="H155">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тёмная кровь на весь отряд: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Тёмная кровь на весь отряд, 3 раунда: лечение каждый ход — сразу 3 стака по 40 % атаки; вдвое сильнее, пока цель ниже 30 % здоровья.</t>
         </is>
       </c>
       <c r="H156">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ужас на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Ужас на всех врагов, 2 раунда: цель не действует, пока не получит удар.</t>
         </is>
       </c>
       <c r="H157">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ослабление на всех врагов: −35 % урона, 4 раунда.</t>
+          <t xml:space="preserve">Ослабление на всех врагов, 4 раунда: −35 % наносимого урона.</t>
         </is>
       </c>
       <c r="H158">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кровожадность всему отряду: +25 % вампиризма, 4 раунда.</t>
+          <t xml:space="preserve">Кровожадность всему отряду, 4 раунда: удары лечат на 25 % нанесённого урона.</t>
         </is>
       </c>
       <c r="H159">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+5 % вампиризма от любого урона.</t>
+          <t xml:space="preserve">Герой лечится на 5 % любого нанесённого урона.</t>
         </is>
       </c>
       <c r="J160" s="3"/>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дебаффы героя держатся на раунд дольше.</t>
+          <t xml:space="preserve">Дебаффы героя — ослабляющие эффекты на врагах — держатся на 1 раунд дольше.</t>
         </is>
       </c>
       <c r="J161" s="3"/>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % урона по целям ниже половины здоровья.</t>
+          <t xml:space="preserve">+10 % урона по целям ниже 50 % здоровья.</t>
         </is>
       </c>
       <c r="J162" s="3"/>
@@ -9627,7 +9627,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Увядание героя лечит его на 20 % урона вместо 10 %.</t>
+          <t xml:space="preserve">Увядание героя (урон каждый ход) лечит его на 20 % урона вместо 10 %.</t>
         </is>
       </c>
       <c r="J163" s="3"/>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Герой лечится на 15 % здоровья.</t>
+          <t xml:space="preserve">Когда герой добил врага, он лечится на 15 % здоровья.</t>
         </is>
       </c>
       <c r="J164" s="3"/>
@@ -9719,14 +9719,14 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Герой остаётся с 1 здоровья, атакующий в ужасе на раунд.</t>
+          <t xml:space="preserve">Когда герой получил смертельный удар (раз за биом), он остаётся с 1 здоровья, а атакующий на 1 раунд впадает в ужас: не действует, пока не получит удар.</t>
         </is>
       </c>
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">удар смертелен для героя — раз за биом</t>
+          <t xml:space="preserve">герой получил смертельный удар — раз за биом</t>
         </is>
       </c>
       <c r="M165">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 % шанс вернуть дебафф наложившему.</t>
+          <t xml:space="preserve">Когда на героя наложили дебафф, есть шанс вернуть его наложившему.</t>
         </is>
       </c>
       <c r="H166">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+25 % вампиризма до конца этажа.</t>
+          <t xml:space="preserve">Когда союзник пал, герой до конца этажа лечится на 25 % нанесённого урона.</t>
         </is>
       </c>
       <c r="J167" s="3"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 60 %.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H168">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 100 %; под стужей +15 %.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 100 % атаки; +15 % по целям под стужей (замедление).</t>
         </is>
       </c>
       <c r="H169">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">под стужей +15 %</t>
+          <t xml:space="preserve">+15 % по целям под стужей (замедление)</t>
         </is>
       </c>
       <c r="K169" s="3"/>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 300 %; под стужей +25 %.</t>
+          <t xml:space="preserve">Мощный удар по цели — 300 % атаки; +25 % по цели под стужей (замедление).</t>
         </is>
       </c>
       <c r="H170">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">под стужей +25 %</t>
+          <t xml:space="preserve">+25 % по цели под стужей (замедление)</t>
         </is>
       </c>
       <c r="K170" s="3"/>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит всех своих — по 60 %; целям с тремя стаками родника — ещё щит на 10 % здоровья.</t>
+          <t xml:space="preserve">Лечит всех своих — по 60 % атаки; целям с 3 стаками родника (лечение каждый ход) — ещё щит на 10 % здоровья.</t>
         </is>
       </c>
       <c r="H171">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">целям с тремя стаками родника — ещё щит на 10 % здоровья</t>
+          <t xml:space="preserve">целям с 3 стаками родника (лечение каждый ход) — ещё щит на 10 % здоровья</t>
         </is>
       </c>
       <c r="K171" s="3"/>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит троих самых раненых — по 100 %; с родником +15 %.</t>
+          <t xml:space="preserve">Лечит троих самых раненых — по 100 % атаки; +15 % целям с родником (лечение каждый ход).</t>
         </is>
       </c>
       <c r="H172">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">с родником +15 %</t>
+          <t xml:space="preserve">+15 % целям с родником (лечение каждый ход)</t>
         </is>
       </c>
       <c r="K172" s="3"/>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сильно лечит самого раненого — 300 %; с родником +25 %.</t>
+          <t xml:space="preserve">Сильно лечит самого раненого — 300 % атаки; +25 % цели с родником (лечение каждый ход).</t>
         </is>
       </c>
       <c r="H173">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">с родником +25 %</t>
+          <t xml:space="preserve">+25 % цели с родником (лечение каждый ход)</t>
         </is>
       </c>
       <c r="K173" s="3"/>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит всем своим — по 50 %.</t>
+          <t xml:space="preserve">Щит всем своим — по 50 % атаки.</t>
         </is>
       </c>
       <c r="H174">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит троим самым раненым — по 80 %.</t>
+          <t xml:space="preserve">Щит троим самым раненым — по 80 % атаки.</t>
         </is>
       </c>
       <c r="H175">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит самому раненому — 200 %; кто бьёт по щиту, получает стужу на раунд.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 200 % атаки; кто бьёт по щиту, получает стужу на 1 раунд: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H176">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">кто бьёт по щиту, получает стужу на раунд</t>
+          <t xml:space="preserve">кто бьёт по щиту, получает стужу на 1 раунд: −30 % скорости, цель ходит позже</t>
         </is>
       </c>
       <c r="K176" s="3"/>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обморожение на всех врагов: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Обморожение на всех врагов, 2 раунда: урон 20 % атаки каждый ход; с первым же стаком — стужа на 4 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H177">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обморожение на трёх врагов: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Обморожение на трёх врагов, 3 раунда: урон 30 % атаки каждый ход, до 2 стаков; на 2 стаках — стужа на 4 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H178">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обморожение на цель: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Обморожение на цель, 3 раунда: урон 40 % атаки каждый ход, до 3 стаков; на 3 стаках — стужа на 4 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H179">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Родник на всех своих: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Родник на всех своих, 2 раунда: лечение 20 % атаки каждый ход.</t>
         </is>
       </c>
       <c r="H180">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Родник на троих самых раненых: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Родник на троих самых раненых, 3 раунда: лечение 30 % атаки каждый ход, до 2 стаков.</t>
         </is>
       </c>
       <c r="H181">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Родник на самого раненого: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Родник на самого раненого, 3 раунда: лечение 40 % атаки каждый ход, до 3 стаков.</t>
         </is>
       </c>
       <c r="H182">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заморозка на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Заморозка на всех врагов, 1 раунд: цель не действует, лёд спадает от удара больше 10 % её здоровья.</t>
         </is>
       </c>
       <c r="H183">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заморозка на двух самых опасных врагов, 2 раунда.</t>
+          <t xml:space="preserve">Заморозка на двух самых опасных врагов, 2 раунда: цель не действует, лёд спадает от удара больше 10 % её здоровья.</t>
         </is>
       </c>
       <c r="H184">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заморозка на самого опасного врага, 3 раунда.</t>
+          <t xml:space="preserve">Заморозка на самого опасного врага, 3 раунда: цель не действует, лёд спадает от удара больше 10 % её здоровья.</t>
         </is>
       </c>
       <c r="H185">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стужа на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Стужа на всех врагов, 2 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H186">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стужа на двух врагов, 3 раунда.</t>
+          <t xml:space="preserve">Стужа на двух врагов, 3 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H187">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стужа на цель, 4 раунда.</t>
+          <t xml:space="preserve">Стужа на цель, 4 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H188">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Живая вода всему отряду, 2 раунда.</t>
+          <t xml:space="preserve">Живая вода всему отряду, 2 раунда: +25 % получаемого лечения.</t>
         </is>
       </c>
       <c r="H189">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Живая вода двум самым раненым союзникам, 3 раунда.</t>
+          <t xml:space="preserve">Живая вода двум самым раненым союзникам, 3 раунда: +25 % получаемого лечения.</t>
         </is>
       </c>
       <c r="H190">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Живая вода самому раненому союзнику, 4 раунда.</t>
+          <t xml:space="preserve">Живая вода самому раненому союзнику, 4 раунда: +25 % получаемого лечения.</t>
         </is>
       </c>
       <c r="H191">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупный урон по всем врагам — по 120 %.</t>
+          <t xml:space="preserve">Крупный урон по всем врагам — по 120 % атаки.</t>
         </is>
       </c>
       <c r="H192">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупное лечение всего отряда — по 120 %; и снимает с каждого по одному дебаффу.</t>
+          <t xml:space="preserve">Крупное лечение всего отряда — по 120 % атаки; снимает с каждого 1 вредный эффект.</t>
         </is>
       </c>
       <c r="H193">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">и снимает с каждого по одному дебаффу</t>
+          <t xml:space="preserve">снимает с каждого 1 вредный эффект</t>
         </is>
       </c>
       <c r="K193" s="3"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит всему отряду — по 100 %.</t>
+          <t xml:space="preserve">Крепкий щит всему отряду — по 100 % атаки.</t>
         </is>
       </c>
       <c r="H194">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обморожение на всех врагов: сразу 3 стака по 40 %, 3 раунда; три стака сразу — значит, и стужа сразу.</t>
+          <t xml:space="preserve">Обморожение на всех врагов, 3 раунда: урон каждый ход — сразу 3 стака по 40 % атаки; с ними сразу стужа на 4 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H195">
@@ -11485,11 +11485,7 @@
       <c r="I195">
         <v>40</v>
       </c>
-      <c r="J195" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">три стака сразу — значит, и стужа сразу</t>
-        </is>
-      </c>
+      <c r="J195" s="3"/>
       <c r="K195" s="3"/>
       <c r="L195" s="3"/>
       <c r="M195">
@@ -11535,7 +11531,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Родник на весь отряд: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Родник на весь отряд, 3 раунда: лечение каждый ход — сразу 3 стака по 40 % атаки.</t>
         </is>
       </c>
       <c r="H196">
@@ -11590,7 +11586,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заморозка на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Заморозка на всех врагов, 2 раунда: цель не действует, лёд спадает от удара больше 10 % её здоровья.</t>
         </is>
       </c>
       <c r="H197">
@@ -11642,7 +11638,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стужа на всех врагов: −45 % скорости, 4 раунда.</t>
+          <t xml:space="preserve">Стужа на всех врагов, 4 раунда: −45 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H198">
@@ -11694,7 +11690,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Живая вода всему отряду: +40 % получаемого лечения, 4 раунда.</t>
+          <t xml:space="preserve">Живая вода всему отряду, 4 раунда: +40 % получаемого лечения.</t>
         </is>
       </c>
       <c r="H199">
@@ -11741,7 +11737,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение героя снимает с цели кровотечение.</t>
+          <t xml:space="preserve">Лечение героя снимает с цели кровотечение (урон каждый ход).</t>
         </is>
       </c>
       <c r="J200" s="3"/>
@@ -11802,7 +11798,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % лечения по целям ниже половины здоровья.</t>
+          <t xml:space="preserve">+10 % лечения по целям ниже 50 % здоровья.</t>
         </is>
       </c>
       <c r="J201" s="3"/>
@@ -11863,7 +11859,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % урона по целям под стужей.</t>
+          <t xml:space="preserve">+10 % урона по целям под стужей (замедление).</t>
         </is>
       </c>
       <c r="J202" s="3"/>
@@ -11907,7 +11903,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Родник героя держится на раунд дольше.</t>
+          <t xml:space="preserve">Родник героя (лечение каждый ход) держится на 1 раунд дольше.</t>
         </is>
       </c>
       <c r="J203" s="3"/>
@@ -11951,7 +11947,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лёд героя спадает только от удара больше 25 % здоровья цели.</t>
+          <t xml:space="preserve">Заморозка героя (пропуск хода) крепче: лёд спадает только от удара больше 25 % здоровья цели вместо 10 %.</t>
         </is>
       </c>
       <c r="J204" s="3"/>
@@ -11995,7 +11991,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пока герой жив, отряд наносит +10 % урона целям под стужей.</t>
+          <t xml:space="preserve">Пока герой жив, отряд наносит +10 % урона целям под стужей (замедление).</t>
         </is>
       </c>
       <c r="J205" s="3"/>
@@ -12039,14 +12035,14 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Родник на этого союзника, 1 стак; не чаще раза в раунд.</t>
+          <t xml:space="preserve">Когда союзник упал ниже 30 % здоровья, он получает родник: лечение 40 % атаки каждый ход, 3 раунда. Не чаще раза в раунд.</t>
         </is>
       </c>
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">союзник упал ниже 30 % здоровья</t>
+          <t xml:space="preserve">союзник упал ниже 30 % здоровья</t>
         </is>
       </c>
       <c r="M206">
@@ -12087,7 +12083,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 % шанс сразу снять этот дебафф.</t>
+          <t xml:space="preserve">Когда на героя наложили дебафф, есть шанс сразу снять его.</t>
         </is>
       </c>
       <c r="H207">
@@ -12138,7 +12134,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Следующее лечение героя на 20 % сильнее.</t>
+          <t xml:space="preserve">Когда героя вылечили, следующее его лечение на 20 % сильнее.</t>
         </is>
       </c>
       <c r="J208" s="3"/>
@@ -12186,14 +12182,14 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Герой остаётся с 1 здоровья и замерзает на ход; пока он во льду, урон не проходит.</t>
+          <t xml:space="preserve">Когда герой получил смертельный удар (раз за биом), он остаётся с 1 здоровья и на 1 ход покрывается льдом: ход пропускает, но урон по нему не проходит.</t>
         </is>
       </c>
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">удар смертелен для героя — раз за биом</t>
+          <t xml:space="preserve">герой получил смертельный удар — раз за биом</t>
         </is>
       </c>
       <c r="M209">
@@ -12239,7 +12235,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 60 %.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H210">
@@ -12294,7 +12290,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 100 %; под засветкой +15 %.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 100 % атаки; +15 % по целям под засветкой (меньше магической защиты).</t>
         </is>
       </c>
       <c r="H211">
@@ -12305,7 +12301,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">под засветкой +15 %</t>
+          <t xml:space="preserve">+15 % по целям под засветкой (меньше магической защиты)</t>
         </is>
       </c>
       <c r="K211" s="3"/>
@@ -12353,7 +12349,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 300 %; под засветкой +25 %.</t>
+          <t xml:space="preserve">Мощный удар по цели — 300 % атаки; +25 % по цели под засветкой (меньше магической защиты).</t>
         </is>
       </c>
       <c r="H212">
@@ -12364,7 +12360,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">под засветкой +25 %</t>
+          <t xml:space="preserve">+25 % по цели под засветкой (меньше магической защиты)</t>
         </is>
       </c>
       <c r="K212" s="3"/>
@@ -12412,7 +12408,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит всех своих — по 60 %.</t>
+          <t xml:space="preserve">Лечит всех своих — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H213">
@@ -12484,7 +12480,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит троих самых раненых — по 100 %; и +10 % защиты целям на 2 раунда.</t>
+          <t xml:space="preserve">Лечит троих самых раненых — по 100 % атаки; +10 % защиты целям на 2 раунда.</t>
         </is>
       </c>
       <c r="H214">
@@ -12495,7 +12491,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">и +10 % защиты целям на 2 раунда</t>
+          <t xml:space="preserve">+10 % защиты целям на 2 раунда</t>
         </is>
       </c>
       <c r="K214" s="3"/>
@@ -12560,7 +12556,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сильно лечит самого раненого — 300 %; лишнее лечение становится щитом.</t>
+          <t xml:space="preserve">Сильно лечит самого раненого — 300 % атаки; лишнее лечение становится щитом.</t>
         </is>
       </c>
       <c r="H215">
@@ -12636,7 +12632,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит всем своим — по 50 %.</t>
+          <t xml:space="preserve">Щит всем своим — по 50 % атаки.</t>
         </is>
       </c>
       <c r="H216">
@@ -12691,7 +12687,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит троим самым раненым — по 80 %.</t>
+          <t xml:space="preserve">Щит троим самым раненым — по 80 % атаки.</t>
         </is>
       </c>
       <c r="H217">
@@ -12746,7 +12742,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит самому раненому — 200 %.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 200 % атаки.</t>
         </is>
       </c>
       <c r="H218">
@@ -12801,7 +12797,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жжение на всех врагов: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Жжение на всех врагов, 2 раунда: урон 20 % атаки каждый ход; +50 % по цели под засветкой (меньше магической защиты).</t>
         </is>
       </c>
       <c r="H219">
@@ -12856,7 +12852,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жжение на трёх врагов: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Жжение на трёх врагов, 3 раунда: урон 30 % атаки каждый ход, до 2 стаков; +50 % по цели под засветкой (меньше магической защиты).</t>
         </is>
       </c>
       <c r="H220">
@@ -12911,7 +12907,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жжение на цель: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Жжение на цель, 3 раунда: урон 40 % атаки каждый ход, до 3 стаков; +50 % по цели под засветкой (меньше магической защиты).</t>
         </is>
       </c>
       <c r="H221">
@@ -12966,7 +12962,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сияние на всех своих: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Сияние на всех своих, 2 раунда: лечение 20 % атаки каждый ход; лишнее лечение становится щитом.</t>
         </is>
       </c>
       <c r="H222">
@@ -13021,7 +13017,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сияние на троих самых раненых: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Сияние на троих самых раненых, 3 раунда: лечение 30 % атаки каждый ход, до 2 стаков; лишнее лечение становится щитом.</t>
         </is>
       </c>
       <c r="H223">
@@ -13076,7 +13072,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сияние на самого раненого: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Сияние на самого раненого, 3 раунда: лечение 40 % атаки каждый ход, до 3 стаков; лишнее лечение становится щитом.</t>
         </is>
       </c>
       <c r="H224">
@@ -13148,7 +13144,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ослепление на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Ослепление на всех врагов, 1 раунд: удары цели уходят мимо, лечение и щиты работают.</t>
         </is>
       </c>
       <c r="H225">
@@ -13200,7 +13196,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ослепление на двух самых опасных врагов, 2 раунда.</t>
+          <t xml:space="preserve">Ослепление на двух самых опасных врагов, 2 раунда: удары цели уходят мимо, лечение и щиты работают.</t>
         </is>
       </c>
       <c r="H226">
@@ -13252,7 +13248,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ослепление на самого опасного врага, 3 раунда.</t>
+          <t xml:space="preserve">Ослепление на самого опасного врага, 3 раунда: удары цели уходят мимо, лечение и щиты работают.</t>
         </is>
       </c>
       <c r="H227">
@@ -13321,7 +13317,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Засветка на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Засветка на всех врагов, 2 раунда: −30 % магической защиты.</t>
         </is>
       </c>
       <c r="H228">
@@ -13373,7 +13369,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Засветка на двух врагов, 3 раунда.</t>
+          <t xml:space="preserve">Засветка на двух врагов, 3 раунда: −30 % магической защиты.</t>
         </is>
       </c>
       <c r="H229">
@@ -13425,7 +13421,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Засветка на цель, 4 раунда.</t>
+          <t xml:space="preserve">Засветка на цель, 4 раунда: −30 % магической защиты.</t>
         </is>
       </c>
       <c r="H230">
@@ -13494,7 +13490,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отблеск всему отряду, 2 раунда.</t>
+          <t xml:space="preserve">Отблеск всему отряду, 2 раунда: +20 % физической и магической защиты.</t>
         </is>
       </c>
       <c r="H231">
@@ -13546,7 +13542,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отблеск двум самым раненым союзникам, 3 раунда.</t>
+          <t xml:space="preserve">Отблеск двум самым раненым союзникам, 3 раунда: +20 % физической и магической защиты.</t>
         </is>
       </c>
       <c r="H232">
@@ -13598,7 +13594,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отблеск самому раненому союзнику, 4 раунда.</t>
+          <t xml:space="preserve">Отблеск самому раненому союзнику, 4 раунда: +20 % физической и магической защиты.</t>
         </is>
       </c>
       <c r="H233">
@@ -13650,7 +13646,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупный урон по всем врагам — по 120 %; под засветкой +25 %.</t>
+          <t xml:space="preserve">Крупный урон по всем врагам — по 120 % атаки; +25 % по целям под засветкой (меньше магической защиты).</t>
         </is>
       </c>
       <c r="H234">
@@ -13661,7 +13657,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">под засветкой +25 %</t>
+          <t xml:space="preserve">+25 % по целям под засветкой (меньше магической защиты)</t>
         </is>
       </c>
       <c r="K234" s="3"/>
@@ -13709,7 +13705,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупное лечение самого раненого — 600 %; и 4 раунда цель получает на 25 % меньше урона.</t>
+          <t xml:space="preserve">Крупное лечение самого раненого — 600 % атаки; 4 раунда цель получает на 25 % меньше урона.</t>
         </is>
       </c>
       <c r="H235">
@@ -13720,7 +13716,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">и 4 раунда цель получает на 25 % меньше урона</t>
+          <t xml:space="preserve">4 раунда цель получает на 25 % меньше урона</t>
         </is>
       </c>
       <c r="K235" s="3"/>
@@ -13785,7 +13781,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит всему отряду — по 100 %.</t>
+          <t xml:space="preserve">Крепкий щит всему отряду — по 100 % атаки.</t>
         </is>
       </c>
       <c r="H236">
@@ -13840,7 +13836,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жжение на всех врагов: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Жжение на всех врагов, 3 раунда: урон каждый ход — сразу 3 стака по 40 % атаки; +50 % по цели под засветкой (меньше магической защиты).</t>
         </is>
       </c>
       <c r="H237">
@@ -13895,7 +13891,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сияние на весь отряд: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Сияние на весь отряд, 3 раунда: лечение каждый ход — сразу 3 стака по 40 % атаки; лишнее лечение становится щитом.</t>
         </is>
       </c>
       <c r="H238">
@@ -13950,7 +13946,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ослепление на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Ослепление на всех врагов, 2 раунда: удары цели уходят мимо, лечение и щиты работают.</t>
         </is>
       </c>
       <c r="H239">
@@ -14002,7 +13998,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Засветка на всех врагов: −45 % магической защиты, 4 раунда.</t>
+          <t xml:space="preserve">Засветка на всех врагов, 4 раунда: −45 % магической защиты.</t>
         </is>
       </c>
       <c r="H240">
@@ -14054,7 +14050,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отблеск всему отряду: +30 % физической и магической защиты, 4 раунда.</t>
+          <t xml:space="preserve">Отблеск всему отряду, 4 раунда: +30 % физической и магической защиты.</t>
         </is>
       </c>
       <c r="H241">
@@ -14101,7 +14097,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % защиты союзнику с сиянием.</t>
+          <t xml:space="preserve">Союзник под сиянием героя (лечение каждый ход) получает +10 % защиты.</t>
         </is>
       </c>
       <c r="J242" s="3"/>
@@ -14162,7 +14158,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слепота и ослепление на отряде спадают на раунд раньше.</t>
+          <t xml:space="preserve">Слепота (промахи) и ослепление (удары мимо) на отряде спадают на 1 раунд раньше.</t>
         </is>
       </c>
       <c r="J243" s="3"/>
@@ -14223,7 +14219,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % урона по целям под засветкой.</t>
+          <t xml:space="preserve">+10 % урона по целям под засветкой (меньше магической защиты).</t>
         </is>
       </c>
       <c r="J244" s="3"/>
@@ -14267,7 +14263,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сияние героя держится на раунд дольше.</t>
+          <t xml:space="preserve">Сияние героя (лечение каждый ход) держится на 1 раунд дольше.</t>
         </is>
       </c>
       <c r="J245" s="3"/>
@@ -14311,7 +14307,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Союзник получает щит на 10 % здоровья.</t>
+          <t xml:space="preserve">Когда по союзнику прошёл крит, этот союзник получает щит на 10 % здоровья.</t>
         </is>
       </c>
       <c r="J246" s="3"/>
@@ -14359,7 +14355,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лишнее лечение становится щитом.</t>
+          <t xml:space="preserve">Когда героя вылечили, лишнее лечение становится щитом.</t>
         </is>
       </c>
       <c r="J247" s="3"/>
@@ -14407,7 +14403,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Весь отряд лечится на 20 % здоровья.</t>
+          <t xml:space="preserve">Когда союзник пал, весь отряд лечится на 20 % здоровья.</t>
         </is>
       </c>
       <c r="J248" s="3"/>
@@ -14455,7 +14451,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 % шанс ослепить этого врага на раунд.</t>
+          <t xml:space="preserve">Когда враг применил ульту, есть шанс наложить на него ослепление на 1 раунд: его удары уходят мимо.</t>
         </is>
       </c>
       <c r="H249">
@@ -14511,7 +14507,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 60 %.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H250">
@@ -14566,7 +14562,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 100 %; под истечением +15 %.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 100 % атаки; +15 % по целям под истечением (способности срабатывают реже).</t>
         </is>
       </c>
       <c r="H251">
@@ -14577,7 +14573,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">под истечением +15 %</t>
+          <t xml:space="preserve">+15 % по целям под истечением (способности срабатывают реже)</t>
         </is>
       </c>
       <c r="K251" s="3"/>
@@ -14625,7 +14621,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 300 %; под истечением +25 %.</t>
+          <t xml:space="preserve">Мощный удар по цели — 300 % атаки; +25 % по цели под истечением (способности срабатывают реже).</t>
         </is>
       </c>
       <c r="H252">
@@ -14636,7 +14632,7 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">под истечением +25 %</t>
+          <t xml:space="preserve">+25 % по цели под истечением (способности срабатывают реже)</t>
         </is>
       </c>
       <c r="K252" s="3"/>
@@ -14684,7 +14680,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит всех своих — по 60 %.</t>
+          <t xml:space="preserve">Лечит всех своих — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H253">
@@ -14756,7 +14752,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит троих самых раненых — по 100 %; с обратным ходом +20 %.</t>
+          <t xml:space="preserve">Лечит троих самых раненых — по 100 % атаки; +20 % целям с обратным ходом (лечение каждый ход).</t>
         </is>
       </c>
       <c r="H254">
@@ -14767,7 +14763,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">с обратным ходом +20 %</t>
+          <t xml:space="preserve">+20 % целям с обратным ходом (лечение каждый ход)</t>
         </is>
       </c>
       <c r="K254" s="3"/>
@@ -14832,7 +14828,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сильно лечит самого раненого — 300 %; обновляет длительность всех лечений по времени на цели.</t>
+          <t xml:space="preserve">Сильно лечит самого раненого — 300 % атаки; обновляет длительность всех эффектов лечения на цели.</t>
         </is>
       </c>
       <c r="H255">
@@ -14843,7 +14839,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">обновляет длительность всех лечений по времени на цели</t>
+          <t xml:space="preserve">обновляет длительность всех эффектов лечения на цели</t>
         </is>
       </c>
       <c r="K255" s="3"/>
@@ -14908,7 +14904,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит всем своим — по 50 %.</t>
+          <t xml:space="preserve">Щит всем своим — по 50 % атаки.</t>
         </is>
       </c>
       <c r="H256">
@@ -14963,7 +14959,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит троим самым раненым — по 80 %.</t>
+          <t xml:space="preserve">Щит троим самым раненым — по 80 % атаки.</t>
         </is>
       </c>
       <c r="H257">
@@ -15018,7 +15014,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит самому раненому — 200 %.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 200 % атаки.</t>
         </is>
       </c>
       <c r="H258">
@@ -15073,7 +15069,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Старение на всех врагов: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Старение на всех врагов, 2 раунда: урон 20 % атаки каждый ход; с каждым ходом сильнее на 10 % атаки.</t>
         </is>
       </c>
       <c r="H259">
@@ -15128,7 +15124,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Старение на трёх врагов: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Старение на трёх врагов, 3 раунда: урон 30 % атаки каждый ход, до 2 стаков; с каждым ходом сильнее на 10 % атаки.</t>
         </is>
       </c>
       <c r="H260">
@@ -15183,7 +15179,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Старение на цель: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Старение на цель, 3 раунда: урон 40 % атаки каждый ход, до 3 стаков; с каждым ходом сильнее на 10 % атаки.</t>
         </is>
       </c>
       <c r="H261">
@@ -15238,7 +15234,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обратный ход на всех своих: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Обратный ход на всех своих, 2 раунда: лечение 20 % атаки каждый ход; с каждым ходом сильнее на 10 % атаки.</t>
         </is>
       </c>
       <c r="H262">
@@ -15293,7 +15289,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обратный ход на троих самых раненых: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Обратный ход на троих самых раненых, 3 раунда: лечение 30 % атаки каждый ход, до 2 стаков; с каждым ходом сильнее на 10 % атаки.</t>
         </is>
       </c>
       <c r="H263">
@@ -15348,7 +15344,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обратный ход на самого раненого: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Обратный ход на самого раненого, 3 раунда: лечение 40 % атаки каждый ход, до 3 стаков; с каждым ходом сильнее на 10 % атаки.</t>
         </is>
       </c>
       <c r="H264">
@@ -15420,7 +15416,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Остановка на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Остановка на всех врагов, 1 раунд: цель ходит последней в раунде, её ульта не срабатывает.</t>
         </is>
       </c>
       <c r="H265">
@@ -15472,7 +15468,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Остановка на двух самых опасных врагов, 2 раунда.</t>
+          <t xml:space="preserve">Остановка на двух самых опасных врагов, 2 раунда: цель ходит последней в раунде, её ульта не срабатывает.</t>
         </is>
       </c>
       <c r="H266">
@@ -15524,7 +15520,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Остановка на самого опасного врага, 3 раунда.</t>
+          <t xml:space="preserve">Остановка на самого опасного врага, 3 раунда: цель ходит последней в раунде, её ульта не срабатывает.</t>
         </is>
       </c>
       <c r="H267">
@@ -15593,7 +15589,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Истечение на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Истечение на всех врагов, 2 раунда: −33 % к шансам способностей и ульты цели.</t>
         </is>
       </c>
       <c r="H268">
@@ -15645,7 +15641,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Истечение на двух врагов, 3 раунда.</t>
+          <t xml:space="preserve">Истечение на двух врагов, 3 раунда: −33 % к шансам способностей и ульты цели.</t>
         </is>
       </c>
       <c r="H269">
@@ -15697,7 +15693,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Истечение на цель, 4 раунда.</t>
+          <t xml:space="preserve">Истечение на цель, 4 раунда: −33 % к шансам способностей и ульты цели.</t>
         </is>
       </c>
       <c r="H270">
@@ -15766,7 +15762,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ускорение всему отряду, 2 раунда.</t>
+          <t xml:space="preserve">Ускорение всему отряду, 2 раунда: +25 % к шансам способностей и ульты.</t>
         </is>
       </c>
       <c r="H271">
@@ -15818,7 +15814,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ускорение двум самым сильным союзникам, 3 раунда.</t>
+          <t xml:space="preserve">Ускорение двум самым сильным союзникам, 3 раунда: +25 % к шансам способностей и ульты.</t>
         </is>
       </c>
       <c r="H272">
@@ -15870,7 +15866,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ускорение самому сильному союзнику, 4 раунда.</t>
+          <t xml:space="preserve">Ускорение самому сильному союзнику, 4 раунда: +25 % к шансам способностей и ульты.</t>
         </is>
       </c>
       <c r="H273">
@@ -15922,7 +15918,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупный урон по трём врагам — по 200 %.</t>
+          <t xml:space="preserve">Крупный урон по трём врагам — по 200 % атаки.</t>
         </is>
       </c>
       <c r="H274">
@@ -15977,7 +15973,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Возвращает самому раненому всё здоровье, потерянное за последние 2 раунда.</t>
+          <t xml:space="preserve">Возвращает самому раненому всё здоровье, потерянное за последние 2 раунда.</t>
         </is>
       </c>
       <c r="H275">
@@ -16049,7 +16045,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит всему отряду — по 100 %.</t>
+          <t xml:space="preserve">Крепкий щит всему отряду — по 100 % атаки.</t>
         </is>
       </c>
       <c r="H276">
@@ -16104,7 +16100,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Старение на всех врагов: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Старение на всех врагов, 3 раунда: урон каждый ход — сразу 3 стака по 40 % атаки; с каждым ходом сильнее на 10 % атаки.</t>
         </is>
       </c>
       <c r="H277">
@@ -16159,7 +16155,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обратный ход на весь отряд: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Обратный ход на весь отряд, 3 раунда: лечение каждый ход — сразу 3 стака по 40 % атаки; с каждым ходом сильнее на 10 % атаки.</t>
         </is>
       </c>
       <c r="H278">
@@ -16214,7 +16210,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Остановка на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Остановка на всех врагов, 2 раунда: цель ходит последней в раунде, её ульта не срабатывает.</t>
         </is>
       </c>
       <c r="H279">
@@ -16266,7 +16262,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Истечение на всех врагов: шансы способностей и ульты × 1/2, 4 раунда.</t>
+          <t xml:space="preserve">Истечение на всех врагов, 4 раунда: −50 % к шансам способностей и ульты цели.</t>
         </is>
       </c>
       <c r="H280">
@@ -16318,7 +16314,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ускорение всему отряду: шансы способностей и ульты × 1,4, 4 раунда.</t>
+          <t xml:space="preserve">Ускорение всему отряду, 4 раунда: +40 % к шансам способностей и ульты.</t>
         </is>
       </c>
       <c r="H281">
@@ -16365,7 +16361,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каждый пятый свой ход герой лечит самого раненого союзника на 150 %.</t>
+          <t xml:space="preserve">Каждый пятый свой ход герой лечит самого раненого союзника на 150 % атаки.</t>
         </is>
       </c>
       <c r="I282">
@@ -16429,7 +16425,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шанс своей ульты × 1,1.</t>
+          <t xml:space="preserve">Ульта героя срабатывает на 10 % чаще.</t>
         </is>
       </c>
       <c r="J283" s="3"/>
@@ -16490,7 +16486,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % урона по целям под истечением.</t>
+          <t xml:space="preserve">+10 % урона по целям под истечением (способности срабатывают реже).</t>
         </is>
       </c>
       <c r="J284" s="3"/>
@@ -16534,7 +16530,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обратный ход героя держится на раунд дольше.</t>
+          <t xml:space="preserve">Обратный ход героя (лечение каждый ход) держится на 1 раунд дольше.</t>
         </is>
       </c>
       <c r="J285" s="3"/>
@@ -16578,7 +16574,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Старение героя держится на раунд дольше.</t>
+          <t xml:space="preserve">Старение героя (урон каждый ход) держится на 1 раунд дольше.</t>
         </is>
       </c>
       <c r="J286" s="3"/>
@@ -16622,14 +16618,14 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Здоровье героя возвращается к началу раунда.</t>
+          <t xml:space="preserve">Когда герой получил смертельный удар (раз за биом), он не гибнет: его здоровье возвращается к значению на начало раунда.</t>
         </is>
       </c>
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
       <c r="L287" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">удар смертелен для героя — раз за биом</t>
+          <t xml:space="preserve">герой получил смертельный удар — раз за биом</t>
         </is>
       </c>
       <c r="M287">
@@ -16670,7 +16666,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 % шанс остановить этого врага на раунд.</t>
+          <t xml:space="preserve">Когда враг применил ульту, есть шанс наложить на него остановку на 1 раунд: он ходит последним, его ульта не срабатывает.</t>
         </is>
       </c>
       <c r="H288">
@@ -16721,7 +16717,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 % шанс в следующем раунде ходить первым.</t>
+          <t xml:space="preserve">Когда героя ударили, есть шанс в следующем раунде ходить первым.</t>
         </is>
       </c>
       <c r="H289">
@@ -16772,7 +16768,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 % шанс снять контроль в начале своего хода.</t>
+          <t xml:space="preserve">Когда на героя наложили контроль, есть шанс снять его в начале своего хода.</t>
         </is>
       </c>
       <c r="H290">
@@ -16828,7 +16824,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 60 %.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H291">
@@ -16883,7 +16879,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 100 %; с кровотечением +15 %.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 100 % атаки; +15 % по целям с кровотечением (урон каждый ход).</t>
         </is>
       </c>
       <c r="H292">
@@ -16894,7 +16890,7 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">с кровотечением +15 %</t>
+          <t xml:space="preserve">+15 % по целям с кровотечением (урон каждый ход)</t>
         </is>
       </c>
       <c r="K292" s="3"/>
@@ -16942,7 +16938,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 300 %; со сломом строя +25 %.</t>
+          <t xml:space="preserve">Мощный удар по цели — 300 % атаки; +25 % по цели под сломом строя (слабее криты и уклонение).</t>
         </is>
       </c>
       <c r="H293">
@@ -16953,7 +16949,7 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">со сломом строя +25 %</t>
+          <t xml:space="preserve">+25 % по цели под сломом строя (слабее криты и уклонение)</t>
         </is>
       </c>
       <c r="K293" s="3"/>
@@ -17001,7 +16997,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит всех своих — по 60 %.</t>
+          <t xml:space="preserve">Лечит всех своих — по 60 % атаки.</t>
         </is>
       </c>
       <c r="H294">
@@ -17056,7 +17052,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит троих самых раненых — по 100 %; и снимает с целей кровотечение.</t>
+          <t xml:space="preserve">Лечит троих самых раненых — по 100 % атаки; снимает с целей кровотечение (урон каждый ход).</t>
         </is>
       </c>
       <c r="H295">
@@ -17067,7 +17063,7 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">и снимает с целей кровотечение</t>
+          <t xml:space="preserve">снимает с целей кровотечение (урон каждый ход)</t>
         </is>
       </c>
       <c r="K295" s="3"/>
@@ -17132,7 +17128,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сильно лечит самого раненого — 300 %; вдвое сильнее, если цель ниже 25 % здоровья.</t>
+          <t xml:space="preserve">Сильно лечит самого раненого — 300 % атаки; вдвое сильнее, если цель ниже 25 % здоровья.</t>
         </is>
       </c>
       <c r="H296">
@@ -17143,7 +17139,7 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">вдвое сильнее, если цель ниже 25 % здоровья</t>
+          <t xml:space="preserve">вдвое сильнее, если цель ниже 25 % здоровья</t>
         </is>
       </c>
       <c r="K296" s="3"/>
@@ -17208,7 +17204,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит всем своим — по 50 %.</t>
+          <t xml:space="preserve">Щит всем своим — по 50 % атаки.</t>
         </is>
       </c>
       <c r="H297">
@@ -17263,7 +17259,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит троим самым раненым — по 80 %.</t>
+          <t xml:space="preserve">Щит троим самым раненым — по 80 % атаки.</t>
         </is>
       </c>
       <c r="H298">
@@ -17318,7 +17314,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит самому раненому — 200 %.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 200 % атаки.</t>
         </is>
       </c>
       <c r="H299">
@@ -17373,7 +17369,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кровотечение на всех врагов: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Кровотечение на всех врагов, 2 раунда: урон 20 % атаки каждый ход; снимает его только лечение, что останавливает кровь.</t>
         </is>
       </c>
       <c r="H300">
@@ -17428,7 +17424,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кровотечение на трёх врагов: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Кровотечение на трёх врагов, 3 раунда: урон 30 % атаки каждый ход, до 2 стаков; снимает его только лечение, что останавливает кровь.</t>
         </is>
       </c>
       <c r="H301">
@@ -17483,7 +17479,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кровотечение на цель: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Кровотечение на цель, 3 раунда: урон 40 % атаки каждый ход, до 3 стаков; снимает его только лечение, что останавливает кровь.</t>
         </is>
       </c>
       <c r="H302">
@@ -17538,7 +17534,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перевязка на всех своих: 20 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Перевязка на всех своих, 2 раунда: лечение 20 % атаки каждый ход; ничем не снимается.</t>
         </is>
       </c>
       <c r="H303">
@@ -17593,7 +17589,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перевязка на троих самых раненых: 30 % за ход, 3 раунда, до 2 стаков.</t>
+          <t xml:space="preserve">Перевязка на троих самых раненых, 3 раунда: лечение 30 % атаки каждый ход, до 2 стаков; ничем не снимается.</t>
         </is>
       </c>
       <c r="H304">
@@ -17665,7 +17661,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перевязка на самого раненого: 40 % за ход, 3 раунда, до 3 стаков.</t>
+          <t xml:space="preserve">Перевязка на самого раненого, 3 раунда: лечение 40 % атаки каждый ход, до 3 стаков; ничем не снимается.</t>
         </is>
       </c>
       <c r="H305">
@@ -17737,7 +17733,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оглушение на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Оглушение на всех врагов, 1 раунд: цель пропускает ход.</t>
         </is>
       </c>
       <c r="H306">
@@ -17789,7 +17785,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оглушение на двух самых опасных врагов, 2 раунда.</t>
+          <t xml:space="preserve">Оглушение на двух самых опасных врагов, 2 раунда: цель пропускает ход.</t>
         </is>
       </c>
       <c r="H307">
@@ -17841,7 +17837,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оглушение на самого опасного врага, 3 раунда.</t>
+          <t xml:space="preserve">Оглушение на самого опасного врага, 3 раунда: цель пропускает ход.</t>
         </is>
       </c>
       <c r="H308">
@@ -17910,7 +17906,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слом строя на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Слом строя на всех врагов, 2 раунда: −25 % критического урона и −10 % уклонения.</t>
         </is>
       </c>
       <c r="H309">
@@ -17962,7 +17958,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слом строя на двух врагов, 3 раунда.</t>
+          <t xml:space="preserve">Слом строя на двух врагов, 3 раунда: −25 % критического урона и −10 % уклонения.</t>
         </is>
       </c>
       <c r="H310">
@@ -18014,7 +18010,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слом строя на цель, 4 раунда.</t>
+          <t xml:space="preserve">Слом строя на цель, 4 раунда: −25 % критического урона и −10 % уклонения.</t>
         </is>
       </c>
       <c r="H311">
@@ -18083,7 +18079,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Боевой дух всему отряду, 2 раунда.</t>
+          <t xml:space="preserve">Боевой дух всему отряду, 2 раунда: +15 % шанса крита.</t>
         </is>
       </c>
       <c r="H312">
@@ -18135,7 +18131,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Боевой дух двум самым сильным союзникам, 3 раунда.</t>
+          <t xml:space="preserve">Боевой дух двум самым сильным союзникам, 3 раунда: +15 % шанса крита.</t>
         </is>
       </c>
       <c r="H313">
@@ -18187,7 +18183,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Боевой дух самому сильному союзнику, 4 раунда.</t>
+          <t xml:space="preserve">Боевой дух самому сильному союзнику, 4 раунда: +15 % шанса крита.</t>
         </is>
       </c>
       <c r="H314">
@@ -18239,7 +18235,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупный урон по цели — 600 %.</t>
+          <t xml:space="preserve">Крупный урон по цели — 600 % атаки.</t>
         </is>
       </c>
       <c r="H315">
@@ -18294,7 +18290,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупное лечение всего отряда — по 120 %.</t>
+          <t xml:space="preserve">Крупное лечение всего отряда — по 120 % атаки.</t>
         </is>
       </c>
       <c r="H316">
@@ -18349,7 +18345,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит всему отряду на 25 % здоровья каждого и снятие контроля со всех.</t>
+          <t xml:space="preserve">Щит всему отряду на 25 % здоровья каждого; снимает со всех контроль — эффекты, что мешают ходить или бить.</t>
         </is>
       </c>
       <c r="H317">
@@ -18421,7 +18417,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кровотечение на всех врагов: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Кровотечение на всех врагов, 3 раунда: урон каждый ход — сразу 3 стака по 40 % атаки; снимает его только лечение, что останавливает кровь.</t>
         </is>
       </c>
       <c r="H318">
@@ -18476,7 +18472,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перевязка на весь отряд: сразу 3 стака по 40 %, 3 раунда.</t>
+          <t xml:space="preserve">Перевязка на весь отряд, 3 раунда: лечение каждый ход — сразу 3 стака по 40 % атаки; ничем не снимается.</t>
         </is>
       </c>
       <c r="H319">
@@ -18531,7 +18527,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оглушение на всех врагов, 2 раунда.</t>
+          <t xml:space="preserve">Оглушение на всех врагов, 2 раунда: цель пропускает ход.</t>
         </is>
       </c>
       <c r="H320">
@@ -18583,7 +18579,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слом строя на всех врагов: −35 % критического урона и −15 % уклонения, 4 раунда.</t>
+          <t xml:space="preserve">Слом строя на всех врагов, 4 раунда: −35 % критического урона и −15 % уклонения.</t>
         </is>
       </c>
       <c r="H321">
@@ -18635,7 +18631,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Боевой дух всему отряду: +25 % шанса крита, 4 раунда.</t>
+          <t xml:space="preserve">Боевой дух всему отряду, 4 раунда: +25 % шанса крита.</t>
         </is>
       </c>
       <c r="H322">
@@ -18682,7 +18678,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % критического урона.</t>
+          <t xml:space="preserve">+10 % критического урона.</t>
         </is>
       </c>
       <c r="J323" s="3"/>
@@ -18743,7 +18739,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обычные атаки игнорируют 10 % физической защиты.</t>
+          <t xml:space="preserve">Обычные атаки героя игнорируют 10 % физической защиты цели.</t>
         </is>
       </c>
       <c r="J324" s="3"/>
@@ -18804,7 +18800,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+10 % урона по целям с кровотечением.</t>
+          <t xml:space="preserve">+10 % урона по целям с кровотечением (урон каждый ход).</t>
         </is>
       </c>
       <c r="J325" s="3"/>
@@ -18848,7 +18844,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">−10 % получаемого периодического урона.</t>
+          <t xml:space="preserve">−10 % получаемого урона от эффектов, что бьют каждый ход.</t>
         </is>
       </c>
       <c r="J326" s="3"/>
@@ -18892,7 +18888,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+15 % урона по целям под любым контролем.</t>
+          <t xml:space="preserve">+15 % урона по целям под любым контролем — эффектом, что мешает ходить или бить.</t>
         </is>
       </c>
       <c r="J327" s="3"/>
@@ -18936,7 +18932,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пока герой жив, отряд получает на 5 % меньше урона.</t>
+          <t xml:space="preserve">Пока герой жив, отряд получает на 5 % меньше урона.</t>
         </is>
       </c>
       <c r="J328" s="3"/>
@@ -18980,7 +18976,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 % шанс ответить обычной атакой.</t>
+          <t xml:space="preserve">Когда героя ударили, есть шанс ответить обычной атакой.</t>
         </is>
       </c>
       <c r="H329">
@@ -19031,14 +19027,14 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+30 % урона.</t>
+          <t xml:space="preserve">Пока здоровье героя ниже 25 %, он наносит на 30 % больше урона.</t>
         </is>
       </c>
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
       <c r="L330" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">здоровье героя ниже 25 %</t>
+          <t xml:space="preserve">здоровье героя ниже 25 %</t>
         </is>
       </c>
       <c r="M330">
@@ -19079,7 +19075,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Этот удар наносит на 50 % меньше урона.</t>
+          <t xml:space="preserve">Первый удар по герою за этаж наносит на 50 % меньше урона.</t>
         </is>
       </c>
       <c r="J331" s="3"/>
@@ -19127,7 +19123,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Следующая атака героя наносит +25 % урона.</t>
+          <t xml:space="preserve">Когда герой нанёс крит, следующая его атака наносит на 25 % больше урона.</t>
         </is>
       </c>
       <c r="J332" s="3"/>
@@ -19180,7 +19176,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удар по цели — 100 %. Если она погибает от него, её золото и дух × 2.</t>
+          <t xml:space="preserve">Удар по цели — 100 % атаки. Если она погибает от него, её золото и дух × 2.</t>
         </is>
       </c>
       <c r="H333">
@@ -19235,7 +19231,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метка на двух врагов, 3 раунда: помеченный при гибели даёт +50 % добычи.</t>
+          <t xml:space="preserve">Помечает двух врагов на 3 раунда: помеченный при гибели даёт +50 % добычи.</t>
         </is>
       </c>
       <c r="H334">
@@ -19287,7 +19283,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 раунда: каждый павший враг даёт +20 % добычи.</t>
+          <t xml:space="preserve">2 раунда каждый павший враг даёт +20 % добычи.</t>
         </is>
       </c>
       <c r="H335">
@@ -19339,7 +19335,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удар по цели — 100 %. Если она погибает от него, шанс базового ресурса с неё +25 %.</t>
+          <t xml:space="preserve">Удар по цели — 100 % атаки. Если она погибает от него, шанс базового ресурса с неё +25 %.</t>
         </is>
       </c>
       <c r="H336">
@@ -19389,7 +19385,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раз за этаж: до конца этажа шанс базового ресурса × 2.</t>
+          <t xml:space="preserve">Раз за этаж: до конца этажа шанс базового ресурса × 2.</t>
         </is>
       </c>
       <c r="H337">
@@ -19436,7 +19432,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раз за этаж: на этом этаже шанс уникального ресурса и второго ключа × 2.</t>
+          <t xml:space="preserve">Раз за этаж: на этом этаже шанс уникального ресурса и второго ключа × 2.</t>
         </is>
       </c>
       <c r="H338">
@@ -19483,7 +19479,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вся добыча этажа × 2.</t>
+          <t xml:space="preserve">Вся добыча этажа × 2.</t>
         </is>
       </c>
       <c r="H339">
@@ -19530,7 +19526,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Золото этажа × 3.</t>
+          <t xml:space="preserve">Золото этажа × 3.</t>
         </is>
       </c>
       <c r="H340">
@@ -19577,7 +19573,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дух этажа × 3.</t>
+          <t xml:space="preserve">Дух этажа × 3.</t>
         </is>
       </c>
       <c r="H341">
@@ -19624,7 +19620,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Этаж даёт базовый ресурс наверняка, а каждая элита — второй ключ.</t>
+          <t xml:space="preserve">Этаж даёт базовый ресурс наверняка, а каждая элита — второй ключ.</t>
         </is>
       </c>
       <c r="H342">
@@ -19671,7 +19667,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+20 % золота отряду.</t>
+          <t xml:space="preserve">+20 % золота отряду.</t>
         </is>
       </c>
       <c r="J343" s="3"/>
@@ -19715,7 +19711,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+25 % духа отряду.</t>
+          <t xml:space="preserve">+25 % духа отряду.</t>
         </is>
       </c>
       <c r="J344" s="3"/>
@@ -19759,7 +19755,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 душа за каждую элиту и +5 за босса — там, где души положены.</t>
+          <t xml:space="preserve">+1 душа за каждую элиту и +5 за босса — там, где души положены.</t>
         </is>
       </c>
       <c r="J345" s="3"/>
@@ -19803,7 +19799,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шанс базового ресурса за этаж × 1,5.</t>
+          <t xml:space="preserve">Шанс базового ресурса за этаж × 1,5.</t>
         </is>
       </c>
       <c r="J346" s="3"/>
@@ -19847,7 +19843,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 % шанс второго ключа ремесла с элиты.</t>
+          <t xml:space="preserve">Шанс 20 % получить с элиты второй ключ ремесла.</t>
         </is>
       </c>
       <c r="J347" s="3"/>
@@ -19891,7 +19887,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+5 % к шансу уникального ресурса босса.</t>
+          <t xml:space="preserve">+5 % к шансу уникального ресурса босса.</t>
         </is>
       </c>
       <c r="J348" s="3"/>
@@ -19935,7 +19931,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 % шанс двойной добычи с любого врага.</t>
+          <t xml:space="preserve">Шанс 5 % на двойную добычу с любого врага.</t>
         </is>
       </c>
       <c r="J349" s="3"/>
@@ -19979,7 +19975,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 к верхней границе ресурсов с рядовых.</t>
+          <t xml:space="preserve">+1 к верхней границе ресурсов с рядовых.</t>
         </is>
       </c>
       <c r="J350" s="3"/>
@@ -20028,7 +20024,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 60 %, горящим +15 %; каждому — стак горения: 24 % за ход, 3 раунда.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 60 % атаки; +15 % по целям под горением; каждому — горение, 3 раунда: урон 24 % атаки каждый ход, до 3 стаков.</t>
         </is>
       </c>
       <c r="H351">
@@ -20087,7 +20083,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 180 %, +25 % за каждый стак горения на ней; себе — жар: +20 % урона на 3 раунда.</t>
+          <t xml:space="preserve">Мощный удар по цели — 180 % атаки; +25 % за каждый стак горения (урон каждый ход) на цели; себе — жар, 3 раунда: +20 % наносимого урона.</t>
         </is>
       </c>
       <c r="H352">
@@ -20146,7 +20142,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит самому раненому — 120 %: кто бьёт по щиту, загорается; метка на цель, 3 раунда.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 120 % атаки; кто бьёт по щиту, получает горение: урон 40 % атаки каждый ход, 3 раунда; метка на цель, 3 раунда: +20 % получаемого урона.</t>
         </is>
       </c>
       <c r="H353">
@@ -20205,7 +20201,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит самого раненого — 180 % и снимает с него кровотечение; ему же — тепло: 24 % за ход, 3 раунда, снимает стужу.</t>
+          <t xml:space="preserve">Сильно лечит самого раненого — 180 % атаки; снимает с цели кровотечение (урон каждый ход); ему же — тепло, 3 раунда: лечение 24 % атаки каждый ход, до 3 стаков; снимает стужу (замедление).</t>
         </is>
       </c>
       <c r="H354">
@@ -20264,7 +20260,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 180 %; паралич цели на 2 раунда.</t>
+          <t xml:space="preserve">Мощный удар по цели — 180 % атаки; ей же — паралич, 2 раунда: цель без обычной атаки — ходит только способностью.</t>
         </is>
       </c>
       <c r="H355">
@@ -20323,7 +20319,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит самому раненому — 120 %; ему же — живица: 21 % за ход, 4 раунда.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 120 % атаки; ему же — живица, 4 раунда: лечение 21 % атаки каждый ход, до 3 стаков.</t>
         </is>
       </c>
       <c r="H356">
@@ -20382,7 +20378,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Яд на трёх врагов: 15 % за ход, 4 раунда; двум первым — осыпание на 2 раунда.</t>
+          <t xml:space="preserve">Яд на трёх врагов, 4 раунда: урон 15 % атаки каждый ход, до 2 стаков; двум первым — осыпание, 2 раунда: −30 % физической защиты.</t>
         </is>
       </c>
       <c r="H357">
@@ -20441,7 +20437,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 60 %, с порезами +15 %; самого опасного врага сбрасывает на 2 раунда: его угроза обнуляется.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 60 % атаки; +15 % по целям с порезами (урон каждый ход); сброс на самого опасного врага, 2 раунда: цель пропускает ход и заново выбирает, кого бить.</t>
         </is>
       </c>
       <c r="H358">
@@ -20500,7 +20496,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 36 %, каждому — стак пореза; слепота на цель, 3 раунда.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 36 % атаки; каждому — порезы: урон 15 % атаки каждый ход, 1 раунд; слепота на цель, 3 раунда: +50 % к шансу промаха.</t>
         </is>
       </c>
       <c r="H359">
@@ -20559,7 +20555,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Свежий ветер на самого раненого: 21 % за ход, 2 раунда; ему же — попутный ветер: +20 % уклонения на 3 раунда.</t>
+          <t xml:space="preserve">Свежий ветер на самого раненого, 2 раунда: лечение 21 % атаки каждый ход, до 4 стаков; ему же — попутный ветер, 3 раунда: +20 % уклонения.</t>
         </is>
       </c>
       <c r="H360">
@@ -20618,7 +20614,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заморозка самого опасного врага на 2 раунда и стужа на 3 раунда: лёд спадёт — холод останется.</t>
+          <t xml:space="preserve">Заморозка на самого опасного врага, 2 раунда: цель не действует, лёд спадает от удара больше 10 % её здоровья; ему же — стужа, 3 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H361">
@@ -20674,7 +20670,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит самому раненому — 120 %: кто бьёт по щиту, получает стужу; ему же — живая вода: +25 % получаемого лечения на 3 раунда.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 120 % атаки; кто бьёт по щиту, получает стужу на 1 раунд: −30 % скорости, цель ходит позже; ему же — живая вода, 3 раунда: +25 % получаемого лечения.</t>
         </is>
       </c>
       <c r="H362">
@@ -20733,7 +20729,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 60 %, под стужей +15 %; двум первым — стужа на 2 раунда.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 60 % атаки; +15 % по целям под стужей; двум первым — стужа, 2 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H363">
@@ -20792,7 +20788,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 60 %, под засветкой +15 %; засветка на цель, 3 раунда.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 60 % атаки; +15 % по целям под засветкой; засветка на цель, 3 раунда: −30 % магической защиты.</t>
         </is>
       </c>
       <c r="H364">
@@ -20851,7 +20847,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит самому раненому — 120 %; ему же — сияние: 24 % за ход, 3 раунда, лишнее лечение становится щитом.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 120 % атаки; ему же — сияние, 3 раунда: лечение 24 % атаки каждый ход, до 3 стаков; лишнее лечение становится щитом.</t>
         </is>
       </c>
       <c r="H365">
@@ -20910,7 +20906,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 180 %, под засветкой +25 %; цель ослеплена на 2 раунда: её удары уходят мимо.</t>
+          <t xml:space="preserve">Мощный удар по цели — 180 % атаки; +25 % по цели под засветкой (меньше магической защиты); ей же — ослепление, 2 раунда: удары цели уходят мимо, лечение и щиты работают.</t>
         </is>
       </c>
       <c r="H366">
@@ -20969,7 +20965,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Увядание на самого опасного врага: 24 % за ход, 3 раунда; он же в ужасе 2 раунда — увядание ужас не сбивает.</t>
+          <t xml:space="preserve">Увядание на самого опасного врага, 3 раунда: урон 24 % атаки каждый ход, до 3 стаков; 10 % урона лечат наложившего; ему же — ужас, 2 раунда: цель не действует, пока не получит удар.</t>
         </is>
       </c>
       <c r="H367">
@@ -21028,7 +21024,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 180 %, +20 % по цели ниже 30 % здоровья; самому раненому союзнику — тёмная кровь: 24 % за ход, 3 раунда.</t>
+          <t xml:space="preserve">Мощный удар по цели — 180 % атаки; +20 % по цели ниже 30 % здоровья; тёмная кровь на самого раненого, 3 раунда: лечение 24 % атаки каждый ход, до 3 стаков; вдвое сильнее, пока цель ниже 30 % здоровья.</t>
         </is>
       </c>
       <c r="H368">
@@ -21087,7 +21083,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит троим самым раненым — по 48 %; двум врагам — ослабление на 2 раунда.</t>
+          <t xml:space="preserve">Щит троим самым раненым — по 48 % атаки; ослабление на двух врагов, 2 раунда: −25 % наносимого урона.</t>
         </is>
       </c>
       <c r="H369">
@@ -21146,7 +21142,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 180 %, под истечением +25 %; цель остановлена на 2 раунда: ходит последней, её ульта не срабатывает.</t>
+          <t xml:space="preserve">Мощный удар по цели — 180 % атаки; +25 % по цели под истечением (способности срабатывают реже); ей же — остановка, 2 раунда: цель ходит последней в раунде, её ульта не срабатывает.</t>
         </is>
       </c>
       <c r="H370">
@@ -21205,7 +21201,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит самому раненому — 120 %; ему же — обратный ход: 24 % за ход, 3 раунда, с каждым ходом сильнее.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 120 % атаки; ему же — обратный ход, 3 раунда: лечение 24 % атаки каждый ход, до 3 стаков; с каждым ходом сильнее на 10 % атаки.</t>
         </is>
       </c>
       <c r="H371">
@@ -21264,7 +21260,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 60 %, под истечением +15 %; двум первым — истечение на 2 раунда.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 60 % атаки; +15 % по целям под истечением; двум первым — истечение, 2 раунда: −33 % к шансам способностей и ульты цели.</t>
         </is>
       </c>
       <c r="H372">
@@ -21323,7 +21319,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 180 %, со сломом строя +25 %; оглушение цели на 2 раунда.</t>
+          <t xml:space="preserve">Мощный удар по цели — 180 % атаки; +25 % по цели под сломом строя (слабее криты и уклонение); ей же — оглушение, 2 раунда: цель пропускает ход.</t>
         </is>
       </c>
       <c r="H373">
@@ -21382,7 +21378,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 60 %, с кровотечением +15 %; самому раненому союзнику — перевязка: 24 % за ход, 3 раунда.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 60 % атаки; +15 % по целям с кровотечением (урон каждый ход); перевязка на самого раненого, 3 раунда: лечение 24 % атаки каждый ход, до 3 стаков; ничем не снимается.</t>
         </is>
       </c>
       <c r="H374">
@@ -21441,7 +21437,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Щит самому раненому — 120 %; слом строя на цель, 3 раунда.</t>
+          <t xml:space="preserve">Крепкий щит самому раненому — 120 % атаки; слом строя на цель, 3 раунда: −25 % критического урона и −10 % уклонения.</t>
         </is>
       </c>
       <c r="H375">
@@ -21500,7 +21496,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 36 %; стужа на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 36 % атаки; стужа на всех врагов, 1 раунд: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H376">
@@ -21559,7 +21555,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мощный удар по цели — 180 %, +25 % за каждый стак горения на ней; цели — осыпание на 3 раунда.</t>
+          <t xml:space="preserve">Мощный удар по цели — 180 % атаки; +25 % за каждый стак горения (урон каждый ход) на цели; ей же — осыпание, 3 раунда: −30 % физической защиты.</t>
         </is>
       </c>
       <c r="H377">
@@ -21618,7 +21614,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 60 %, горящим +15 %; каждому — стак пореза: 15 % за ход, 2 раунда.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 60 % атаки; +15 % по целям под горением (урон каждый ход); им же — порезы, 2 раунда: урон 15 % атаки каждый ход, до 3 стаков.</t>
         </is>
       </c>
       <c r="H378">
@@ -21677,7 +21673,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Паралич на двух самых опасных врагов, 1 раунд; им же — стужа на 2 раунда.</t>
+          <t xml:space="preserve">Паралич на двух самых опасных врагов, 1 раунд: цель без обычной атаки — ходит только способностью; им же — стужа, 2 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H379">
@@ -21733,7 +21729,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осыпание и слепота на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Осыпание на всех врагов, 1 раунд: −30 % физической защиты; слепота на всех врагов, 1 раунд: +50 % к шансу промаха.</t>
         </is>
       </c>
       <c r="H380">
@@ -21789,7 +21785,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт всех врагов — по 36 %; сброс на всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Бьёт всех врагов — по 36 % атаки; сброс на всех врагов, 1 раунд: цель пропускает ход и заново выбирает, кого бить.</t>
         </is>
       </c>
       <c r="H381">
@@ -21848,7 +21844,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечит всех своих — по 36 %; жар всему отряду, 1 раунд.</t>
+          <t xml:space="preserve">Лечит всех своих — по 36 % атаки; жар всему отряду, 1 раунд: +20 % наносимого урона.</t>
         </is>
       </c>
       <c r="H382">
@@ -21907,7 +21903,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ускорение двум самым сильным союзникам и попутный ветер двум самым раненым, 2 раунда.</t>
+          <t xml:space="preserve">Ускорение двум самым сильным союзникам, 2 раунда: +25 % к шансам способностей и ульты; попутный ветер двум самым раненым союзникам, 2 раунда: +20 % уклонения.</t>
         </is>
       </c>
       <c r="H383">
@@ -21963,7 +21959,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Горение и порезы на всех врагов: сразу по 3 стака — 24 % и 18 % за ход, 3 раунда и 2 раунда.</t>
+          <t xml:space="preserve">Горение на всех врагов, 3 раунда: урон каждый ход — сразу 3 стака по 24 % атаки; порезы на всех врагов, 2 раунда: урон каждый ход — сразу 3 стака по 18 % атаки.</t>
         </is>
       </c>
       <c r="H384">
@@ -22022,7 +22018,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крепкий щит всему отряду — по 60 %; заморозка всех врагов, 1 раунд.</t>
+          <t xml:space="preserve">Крепкий щит всему отряду — по 60 % атаки; заморозка на всех врагов, 1 раунд: цель не действует, лёд спадает от удара больше 10 % её здоровья.</t>
         </is>
       </c>
       <c r="H385">
@@ -22081,7 +22077,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жар всему отряду и метка на всех врагов: +30 % урона и +30 % получаемого урона, 3 раунда.</t>
+          <t xml:space="preserve">Жар всему отряду, 3 раунда: +30 % наносимого урона; метка на всех врагов, 3 раунда: +30 % получаемого урона.</t>
         </is>
       </c>
       <c r="H386">
@@ -22137,7 +22133,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каменная кожа и боевой дух всему отряду: −35 % получаемого урона и +25 % шанса крита, 3 раунда.</t>
+          <t xml:space="preserve">Каменная кожа всему отряду, 3 раунда: −35 % получаемого урона; боевой дух всему отряду, 3 раунда: +25 % шанса крита.</t>
         </is>
       </c>
       <c r="H387">
@@ -22238,7 +22234,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">лечение в начале каждого хода цели; снимает с неё стужу</t>
+          <t xml:space="preserve">лечение в начале каждого хода цели; снимает стужу (замедление)</t>
         </is>
       </c>
     </row>
@@ -22282,7 +22278,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+20 % получаемого урона</t>
+          <t xml:space="preserve">+20 % получаемого урона</t>
         </is>
       </c>
     </row>
@@ -22304,7 +22300,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+20 % урона</t>
+          <t xml:space="preserve">+20 % наносимого урона</t>
         </is>
       </c>
     </row>
@@ -22326,7 +22322,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">урон в начале каждого хода цели; на раунд дольше горения, но слабее</t>
+          <t xml:space="preserve">урон в начале каждого хода цели</t>
         </is>
       </c>
     </row>
@@ -22348,7 +22344,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">лечение в начале каждого хода цели; на раунд дольше, но слабее</t>
+          <t xml:space="preserve">лечение в начале каждого хода цели</t>
         </is>
       </c>
     </row>
@@ -22370,7 +22366,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">цель не бьёт обычной атакой — ходит, только если сработает способность</t>
+          <t xml:space="preserve">цель без обычной атаки — ходит только способностью</t>
         </is>
       </c>
     </row>
@@ -22392,7 +22388,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">−30 % физической защиты</t>
+          <t xml:space="preserve">−30 % физической защиты</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22410,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">−25 % получаемого урона</t>
+          <t xml:space="preserve">−25 % получаемого урона</t>
         </is>
       </c>
     </row>
@@ -22436,7 +22432,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">урон в начале каждого хода цели; на стак больше, но на раунд короче и слабее</t>
+          <t xml:space="preserve">урон в начале каждого хода цели</t>
         </is>
       </c>
     </row>
@@ -22458,7 +22454,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">лечение в начале каждого хода цели; на стак больше, но на раунд короче и слабее</t>
+          <t xml:space="preserve">лечение в начале каждого хода цели</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22476,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">цель пропускает ход, её угроза ко всем обнуляется</t>
+          <t xml:space="preserve">цель пропускает ход и заново выбирает, кого бить</t>
         </is>
       </c>
     </row>
@@ -22502,7 +22498,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+50 % промахов</t>
+          <t xml:space="preserve">+50 % к шансу промаха</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22520,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+20 % уклонения</t>
+          <t xml:space="preserve">+20 % уклонения</t>
         </is>
       </c>
     </row>
@@ -22546,7 +22542,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">урон в начале каждого хода цели; 10 % урона лечат наложившего</t>
+          <t xml:space="preserve">урон в начале каждого хода цели; 10 % урона лечат наложившего</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22564,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">лечение в начале каждого хода цели; вдвое сильнее, пока цель ниже 30 % здоровья</t>
+          <t xml:space="preserve">лечение в начале каждого хода цели; вдвое сильнее, пока цель ниже 30 % здоровья</t>
         </is>
       </c>
     </row>
@@ -22590,7 +22586,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">цель не действует; ужас спадает от первого удара по ней</t>
+          <t xml:space="preserve">цель не действует, пока не получит удар</t>
         </is>
       </c>
     </row>
@@ -22612,7 +22608,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">−25 % урона</t>
+          <t xml:space="preserve">−25 % наносимого урона</t>
         </is>
       </c>
     </row>
@@ -22634,7 +22630,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+15 % вампиризма</t>
+          <t xml:space="preserve">удары лечат на 15 % нанесённого урона</t>
         </is>
       </c>
     </row>
@@ -22656,7 +22652,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">урон в начале каждого хода цели; на трёх стаках цель получает стужу</t>
+          <t xml:space="preserve">урон в начале каждого хода цели; на пределе стаков цель получает стужу (замедление)</t>
         </is>
       </c>
     </row>
@@ -22700,7 +22696,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">цель не действует; лёд спадает от удара больше 10 % её здоровья</t>
+          <t xml:space="preserve">цель не действует, лёд спадает от удара больше 10 % её здоровья</t>
         </is>
       </c>
     </row>
@@ -22722,7 +22718,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">−30 % скорости: цель ходит позже</t>
+          <t xml:space="preserve">−30 % скорости, цель ходит позже</t>
         </is>
       </c>
     </row>
@@ -22744,7 +22740,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+25 % получаемого лечения</t>
+          <t xml:space="preserve">+25 % получаемого лечения</t>
         </is>
       </c>
     </row>
@@ -22766,7 +22762,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">урон в начале каждого хода цели; +50 % по цели под засветкой</t>
+          <t xml:space="preserve">урон в начале каждого хода цели; +50 % по цели под засветкой (меньше магической защиты)</t>
         </is>
       </c>
     </row>
@@ -22788,7 +22784,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">лечение в начале каждого хода цели; лишнее становится щитом</t>
+          <t xml:space="preserve">лечение в начале каждого хода цели; лишнее лечение становится щитом</t>
         </is>
       </c>
     </row>
@@ -22810,7 +22806,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">удары цели — обычные и способности — уходят мимо; лечение и щиты работают</t>
+          <t xml:space="preserve">удары цели уходят мимо, лечение и щиты работают</t>
         </is>
       </c>
     </row>
@@ -22832,7 +22828,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">−30 % магической защиты</t>
+          <t xml:space="preserve">−30 % магической защиты</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22850,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+20 % физической и магической защиты</t>
+          <t xml:space="preserve">+20 % физической и магической защиты</t>
         </is>
       </c>
     </row>
@@ -22876,7 +22872,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">урон в начале каждого хода цели; с каждым ходом сильнее на 10 пунктов коэффициента</t>
+          <t xml:space="preserve">урон в начале каждого хода цели; с каждым ходом сильнее на 10 % атаки</t>
         </is>
       </c>
     </row>
@@ -22898,7 +22894,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">лечение в начале каждого хода цели; с каждым ходом сильнее на 10 пунктов коэффициента</t>
+          <t xml:space="preserve">лечение в начале каждого хода цели; с каждым ходом сильнее на 10 % атаки</t>
         </is>
       </c>
     </row>
@@ -22942,7 +22938,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">шансы способностей и ульты цели × 2/3</t>
+          <t xml:space="preserve">−33 % к шансам способностей и ульты цели</t>
         </is>
       </c>
     </row>
@@ -22964,7 +22960,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">шансы способностей и ульты × 1,25</t>
+          <t xml:space="preserve">+25 % к шансам способностей и ульты</t>
         </is>
       </c>
     </row>
@@ -22986,7 +22982,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">урон в начале каждого хода цели; магией не снимается — только лечением, которое останавливает кровь</t>
+          <t xml:space="preserve">урон в начале каждого хода цели; снимает его только лечение, что останавливает кровь</t>
         </is>
       </c>
     </row>
@@ -23008,7 +23004,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">лечение в начале каждого хода цели; не снимается ничем</t>
+          <t xml:space="preserve">лечение в начале каждого хода цели; ничем не снимается</t>
         </is>
       </c>
     </row>
@@ -23052,7 +23048,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">−25 % критического урона и −10 % уклонения</t>
+          <t xml:space="preserve">−25 % критического урона и −10 % уклонения</t>
         </is>
       </c>
     </row>
@@ -23074,7 +23070,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+15 % шанса крита</t>
+          <t xml:space="preserve">+15 % шанса крита</t>
         </is>
       </c>
     </row>

--- a/source-data/Enerium_Способности_элементов.xlsx
+++ b/source-data/Enerium_Способности_элементов.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Таблица автора" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Способности'!$A$1:$R$387</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Способности'!$A$1:$R$398</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Эффекты школ'!$A$1:$D$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ступени целей'!$A$1:$F$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Наборы героев'!$A$1:$P$361</definedName>
@@ -142,7 +142,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вся библиотека способностей игры — 386 записей: семь школ и «Без школы» по восемь видов в трёх ступенях целей, ульты, пассивки и реакции, общий набор фарма (ADR-0015), сочетания — способности из двух — и черты (ADR-0050).</t>
+          <t xml:space="preserve">Вся библиотека способностей игры — 397 записей: семь школ и «Без школы» по восемь видов в трёх ступенях целей, ульты, пассивки и реакции, общий набор фарма (ADR-0015), сочетания — способности из двух — и черты (ADR-0050).</t>
         </is>
       </c>
     </row>
@@ -195,7 +195,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-06 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -207,7 +207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">278287cae2578fab — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">30601548a2722a37 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -244,7 +244,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">386 строк. Шанс в ходе — доля хода, б. п. из 10 000; у героя её поправляет редкость. Носителей — герои состава и враги, у кого способность в наборе. Сочетание — способность из двух записей: обе части действуют за один ход, коэффициент — первой части.</t>
+          <t xml:space="preserve">397 строк. Шанс в ходе — доля хода, б. п. из 10 000; у героя её поправляет редкость. Носителей — герои состава и враги, у кого способность в наборе. Сочетание — способность из двух записей: обе части действуют за один ход, коэффициент — первой части.</t>
         </is>
       </c>
     </row>
@@ -336,8 +336,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
@@ -360,7 +360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R387"/>
+  <dimension ref="A1:R398"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запрет способностей на двух самых опасных врагов, 2 раунда: цель бьёт только обычной атакой.</t>
+          <t xml:space="preserve">Запрет способностей на двух врагов, которые ходят следующими, 2 раунда: цель бьёт только обычной атакой.</t>
         </is>
       </c>
       <c r="H18">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запрет способностей на самого опасного врага, 3 раунда: цель бьёт только обычной атакой.</t>
+          <t xml:space="preserve">Запрет способностей на врага, который ходит следующим, 3 раунда: цель бьёт только обычной атакой.</t>
         </is>
       </c>
       <c r="H19">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Паралич на двух самых опасных врагов, 2 раунда: цель без обычной атаки — ходит только способностью.</t>
+          <t xml:space="preserve">Паралич на двух врагов, которые ходят следующими, 2 раунда: цель без обычной атаки — ходит только способностью.</t>
         </is>
       </c>
       <c r="H59">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Паралич на самого опасного врага, 3 раунда: цель без обычной атаки — ходит только способностью.</t>
+          <t xml:space="preserve">Паралич на врага, который ходит следующим, 3 раунда: цель без обычной атаки — ходит только способностью.</t>
         </is>
       </c>
       <c r="H60">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сброс на двух самых опасных врагов, 2 раунда: цель пропускает ход и заново выбирает, кого бить.</t>
+          <t xml:space="preserve">Сброс на двух врагов, которые ходят следующими, 2 раунда: цель пропускает ход и заново выбирает, кого бить.</t>
         </is>
       </c>
       <c r="H102">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сброс на самого опасного врага, 3 раунда: цель пропускает ход и заново выбирает, кого бить.</t>
+          <t xml:space="preserve">Сброс на врага, который ходит следующим, 3 раунда: цель пропускает ход и заново выбирает, кого бить.</t>
         </is>
       </c>
       <c r="H103">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ужас на двух самых опасных врагов, 2 раунда: цель не действует, пока не получит удар.</t>
+          <t xml:space="preserve">Ужас на двух врагов, которые ходят следующими, 2 раунда: цель не действует, пока не получит удар.</t>
         </is>
       </c>
       <c r="H144">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ужас на самого опасного врага, 3 раунда: цель не действует, пока не получит удар.</t>
+          <t xml:space="preserve">Ужас на врага, который ходит следующим, 3 раунда: цель не действует, пока не получит удар.</t>
         </is>
       </c>
       <c r="H145">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заморозка на двух самых опасных врагов, 2 раунда: цель не действует, лёд спадает от удара больше 10 % её здоровья.</t>
+          <t xml:space="preserve">Заморозка на двух врагов, которые ходят следующими, 2 раунда: цель не действует, лёд спадает от удара больше 10 % её здоровья.</t>
         </is>
       </c>
       <c r="H184">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заморозка на самого опасного врага, 3 раунда: цель не действует, лёд спадает от удара больше 10 % её здоровья.</t>
+          <t xml:space="preserve">Заморозка на врага, который ходит следующим, 3 раунда: цель не действует, лёд спадает от удара больше 10 % её здоровья.</t>
         </is>
       </c>
       <c r="H185">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ослепление на двух самых опасных врагов, 2 раунда: удары цели уходят мимо, лечение и щиты работают.</t>
+          <t xml:space="preserve">Ослепление на двух врагов, которые ходят следующими, 2 раунда: удары цели уходят мимо, лечение и щиты работают.</t>
         </is>
       </c>
       <c r="H226">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ослепление на самого опасного врага, 3 раунда: удары цели уходят мимо, лечение и щиты работают.</t>
+          <t xml:space="preserve">Ослепление на врага, который ходит следующим, 3 раунда: удары цели уходят мимо, лечение и щиты работают.</t>
         </is>
       </c>
       <c r="H227">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Остановка на двух самых опасных врагов, 2 раунда: цель ходит последней в раунде, её ульта не срабатывает.</t>
+          <t xml:space="preserve">Остановка на двух врагов, которые ходят следующими, 2 раунда: цель ходит последней в раунде, её ульта не срабатывает.</t>
         </is>
       </c>
       <c r="H266">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Остановка на самого опасного врага, 3 раунда: цель ходит последней в раунде, её ульта не срабатывает.</t>
+          <t xml:space="preserve">Остановка на врага, который ходит следующим, 3 раунда: цель ходит последней в раунде, её ульта не срабатывает.</t>
         </is>
       </c>
       <c r="H267">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оглушение на двух самых опасных врагов, 2 раунда: цель пропускает ход.</t>
+          <t xml:space="preserve">Оглушение на двух врагов, которые ходят следующими, 2 раунда: цель пропускает ход.</t>
         </is>
       </c>
       <c r="H307">
@@ -17837,7 +17837,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оглушение на самого опасного врага, 3 раунда: цель пропускает ход.</t>
+          <t xml:space="preserve">Оглушение на врага, который ходит следующим, 3 раунда: цель пропускает ход.</t>
         </is>
       </c>
       <c r="H308">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бьёт трёх врагов — по 60 % атаки; +15 % по целям с порезами (урон каждый ход); сброс на самого опасного врага, 2 раунда: цель пропускает ход и заново выбирает, кого бить.</t>
+          <t xml:space="preserve">Бьёт трёх врагов — по 60 % атаки; +15 % по целям с порезами (урон каждый ход); сброс на врага, который ходит следующим, 2 раунда: цель пропускает ход и заново выбирает, кого бить.</t>
         </is>
       </c>
       <c r="H358">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заморозка на самого опасного врага, 2 раунда: цель не действует, лёд спадает от удара больше 10 % её здоровья; ему же — стужа, 3 раунда: −30 % скорости, цель ходит позже.</t>
+          <t xml:space="preserve">Заморозка на врага, который ходит следующим, 2 раунда: цель не действует, лёд спадает от удара больше 10 % её здоровья; ему же — стужа, 3 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H361">
@@ -20965,7 +20965,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Увядание на самого опасного врага, 3 раунда: урон 24 % атаки каждый ход, до 3 стаков; 10 % урона лечат наложившего; ему же — ужас, 2 раунда: цель не действует, пока не получит удар.</t>
+          <t xml:space="preserve">Увядание на врага, который ходит следующим, 3 раунда: урон 24 % атаки каждый ход, до 3 стаков; 10 % урона лечат наложившего; ему же — ужас, 2 раунда: цель не действует, пока не получит удар.</t>
         </is>
       </c>
       <c r="H367">
@@ -21673,7 +21673,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Паралич на двух самых опасных врагов, 1 раунд: цель без обычной атаки — ходит только способностью; им же — стужа, 2 раунда: −30 % скорости, цель ходит позже.</t>
+          <t xml:space="preserve">Паралич на двух врагов, которые ходят следующими, 1 раунд: цель без обычной атаки — ходит только способностью; им же — стужа, 2 раунда: −30 % скорости, цель ходит позже.</t>
         </is>
       </c>
       <c r="H379">
@@ -22156,8 +22156,528 @@
       </c>
       <c r="R387" s="3"/>
     </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.pas.1</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · пассивка</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">пассивка</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стряхнуть порчу</t>
+        </is>
+      </c>
+      <c r="G388" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каждый второй свой ход начинает с того, что снимает с себя один дебафф.</t>
+        </is>
+      </c>
+      <c r="J388" s="3"/>
+      <c r="K388" s="3"/>
+      <c r="L388" s="3"/>
+      <c r="M388">
+        <v>18</v>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="R388" s="3"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.pas.2</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · пассивка</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">пассивка</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сбить пламя</t>
+        </is>
+      </c>
+      <c r="G389" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каждый третий свой ход начинает с того, что сбрасывает с себя весь урон по времени — со всеми стаками.</t>
+        </is>
+      </c>
+      <c r="J389" s="3"/>
+      <c r="K389" s="3"/>
+      <c r="L389" s="3"/>
+      <c r="M389">
+        <v>15</v>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="R389" s="3"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.pas.3</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · пассивка</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">пассивка</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дублёная шкура</t>
+        </is>
+      </c>
+      <c r="G390" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Урон по времени по нему слабее на 40 %.</t>
+        </is>
+      </c>
+      <c r="J390" s="3"/>
+      <c r="K390" s="3"/>
+      <c r="L390" s="3"/>
+      <c r="M390">
+        <v>8</v>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="R390" s="3"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.pas.4</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · пассивка</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">пассивка</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Срыв покрова</t>
+        </is>
+      </c>
+      <c r="G391" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каждая третья его обычная атака срывает с цели щит и всё лечение по времени.</t>
+        </is>
+      </c>
+      <c r="J391" s="3"/>
+      <c r="K391" s="3"/>
+      <c r="L391" s="3"/>
+      <c r="M391">
+        <v>6</v>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="R391" s="3"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.pas.5</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · пассивка</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">пассивка</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ненасытность</t>
+        </is>
+      </c>
+      <c r="G392" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10 % нанесённого им урона лечат его самого.</t>
+        </is>
+      </c>
+      <c r="J392" s="3"/>
+      <c r="K392" s="3"/>
+      <c r="L392" s="3"/>
+      <c r="M392">
+        <v>1</v>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">II</t>
+        </is>
+      </c>
+      <c r="R392" s="3"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.react.1</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · реакция</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">реакция</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ярость скованного</t>
+        </is>
+      </c>
+      <c r="G393" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каждый раз, когда он начинает свой ход под контролем, он злится: до конца этажа наносит на 15 % больше урона — и так до +60 %.</t>
+        </is>
+      </c>
+      <c r="J393" s="3"/>
+      <c r="K393" s="3"/>
+      <c r="L393" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">на героя наложили контроль</t>
+        </is>
+      </c>
+      <c r="M393">
+        <v>13</v>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="R393" s="3"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.react.2</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · реакция</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">реакция</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зеркало воли</t>
+        </is>
+      </c>
+      <c r="G394" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Когда на него накладывают контроль, есть шанс, что тот не ляжет, а вернётся наложившему.</t>
+        </is>
+      </c>
+      <c r="H394">
+        <v>2500</v>
+      </c>
+      <c r="J394" s="3"/>
+      <c r="K394" s="3"/>
+      <c r="L394" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">на героя наложили дебафф</t>
+        </is>
+      </c>
+      <c r="M394">
+        <v>7</v>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="R394" s="3"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.react.3</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · реакция</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">реакция</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Глухая оборона</t>
+        </is>
+      </c>
+      <c r="G395" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Когда на него накладывают дебафф, есть шанс, что тот не ляжет.</t>
+        </is>
+      </c>
+      <c r="H395">
+        <v>3000</v>
+      </c>
+      <c r="J395" s="3"/>
+      <c r="K395" s="3"/>
+      <c r="L395" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">на героя наложили дебафф</t>
+        </is>
+      </c>
+      <c r="M395">
+        <v>12</v>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="R395" s="3"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.react.4</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · реакция</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">реакция</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ответный выпад</t>
+        </is>
+      </c>
+      <c r="G396" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Когда его бьют, есть шанс ответить обычной атакой.</t>
+        </is>
+      </c>
+      <c r="H396">
+        <v>2000</v>
+      </c>
+      <c r="J396" s="3"/>
+      <c r="K396" s="3"/>
+      <c r="L396" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">героя ударили</t>
+        </is>
+      </c>
+      <c r="M396">
+        <v>11</v>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">II</t>
+        </is>
+      </c>
+      <c r="R396" s="3"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.react.5</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · реакция</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">реакция</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каменный лоб</t>
+        </is>
+      </c>
+      <c r="G397" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Когда по нему проходит крит, тот наносит на 40 % меньше урона.</t>
+        </is>
+      </c>
+      <c r="J397" s="3"/>
+      <c r="K397" s="3"/>
+      <c r="L397" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">по герою прошёл крит</t>
+        </is>
+      </c>
+      <c r="M397">
+        <v>11</v>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="R397" s="3"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг.react.6</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Черты врагов</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">черта врага · реакция</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">реакция</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мимо бури</t>
+        </is>
+      </c>
+      <c r="G398" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Когда герой применяет ульту, есть шанс уклониться от неё целиком.</t>
+        </is>
+      </c>
+      <c r="H398">
+        <v>3000</v>
+      </c>
+      <c r="J398" s="3"/>
+      <c r="K398" s="3"/>
+      <c r="L398" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">враг применил ульту</t>
+        </is>
+      </c>
+      <c r="M398">
+        <v>11</v>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="R398" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R387"/>
+  <autoFilter ref="A1:R398"/>
 </worksheet>
 </file>
 
@@ -45768,7 +46288,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Замес (Гнев недр); Тяжёлая рука (Осыпание)</t>
+          <t xml:space="preserve">Замес (Гнев недр); Тяжёлая рука (Осыпание); Дублёная шкура · черта</t>
         </is>
       </c>
     </row>
@@ -45805,7 +46325,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Яд; Снять лишнее (Гнев недр)</t>
+          <t xml:space="preserve">Яд; Снять лишнее (Гнев недр); Срыв покрова · черта</t>
         </is>
       </c>
     </row>
@@ -45842,7 +46362,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Напор (Каменный осколок); Плита (Каменный заслон)</t>
+          <t xml:space="preserve">Напор (Каменный осколок); Плита (Каменный заслон); Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -45879,7 +46399,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Меха (Росчерк); Сквозняк (Смерч)</t>
+          <t xml:space="preserve">Меха (Росчерк); Сквозняк (Смерч); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -45916,7 +46436,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заплата (Сердце горы); Шов (Живые соки)</t>
+          <t xml:space="preserve">Заплата (Сердце горы); Шов (Живые соки); Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -45953,7 +46473,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Съём (Раскол); Оцепенение</t>
+          <t xml:space="preserve">Съём (Раскол); Оцепенение; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -45990,7 +46510,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Правка (Гнев недр); Глиняный вал (Тяжёлый обвал); Последний штрих (Погребение) · ульта</t>
+          <t xml:space="preserve">Правка (Гнев недр); Глиняный вал (Тяжёлый обвал); Последний штрих (Погребение) · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -46027,7 +46547,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резец Мастера (Гнев недр); Остановись (Паралич); Сила гор; Окаменение · ульта</t>
+          <t xml:space="preserve">Резец Мастера (Гнев недр); Остановись (Паралич); Сила гор; Окаменение · ульта; Зеркало воли · черта</t>
         </is>
       </c>
     </row>
@@ -46286,7 +46806,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Клык (Гнев недр); Разгон (Паралич)</t>
+          <t xml:space="preserve">Клык (Гнев недр); Разгон (Паралич); Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -46323,7 +46843,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Двойной выстрел (Кровавый смерч); Спуск.b2e2.act</t>
+          <t xml:space="preserve">Двойной выстрел (Кровавый смерч); Спуск.b2e2.act; Срыв покрова · черта</t>
         </is>
       </c>
     </row>
@@ -46360,7 +46880,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Напор (Каменный осколок); Настил (Каменный заслон)</t>
+          <t xml:space="preserve">Напор (Каменный осколок); Настил (Каменный заслон); Дублёная шкура · черта</t>
         </is>
       </c>
     </row>
@@ -46397,7 +46917,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Листопад (Росчерк); Слепящий лист (Пыль в глаза)</t>
+          <t xml:space="preserve">Листопад (Росчерк); Слепящий лист (Пыль в глаза); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -46434,7 +46954,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отвар (Воздушный поток); Оберег (Ветряной покров)</t>
+          <t xml:space="preserve">Отвар (Воздушный поток); Оберег (Ветряной покров); Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -46471,7 +46991,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Спуск.b2e6.act; Лыковые путы (Вихревой сброс)</t>
+          <t xml:space="preserve">Спуск.b2e6.act; Лыковые путы (Вихревой сброс); Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -46508,7 +47028,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тяжёлая лапа (Гнев недр); Спуск.b2b1.ult · ульта; Спуск.b2b1.pas</t>
+          <t xml:space="preserve">Тяжёлая лапа (Гнев недр); Спуск.b2b1.ult · ульта; Спуск.b2b1.pas; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -46545,7 +47065,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вихрь листвы (Росчерк); Пыльца (Пыльная буря); Стрела ветра (Кровавый смерч); Лес в движении (Ураган) · ульта</t>
+          <t xml:space="preserve">Вихрь листвы (Росчерк); Пыльца (Пыльная буря); Стрела ветра (Кровавый смерч); Лес в движении (Ураган) · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -46804,7 +47324,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бронзовый молоток (Гнев недр); Разобрать (Осыпание)</t>
+          <t xml:space="preserve">Бронзовый молоток (Гнев недр); Разобрать (Осыпание); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -46841,7 +47361,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жвалы (Гнев недр); Рунная стружка (Яд)</t>
+          <t xml:space="preserve">Жвалы (Гнев недр); Рунная стружка (Яд); Ненасытность · черта</t>
         </is>
       </c>
     </row>
@@ -46878,7 +47398,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плита (Каменный заслон); Удар щитом (Паралич)</t>
+          <t xml:space="preserve">Плита (Каменный заслон); Удар щитом (Паралич); Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -46915,7 +47435,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чтение вслух (Росчерк); Разряд (Кровавый смерч)</t>
+          <t xml:space="preserve">Чтение вслух (Росчерк); Разряд (Кровавый смерч); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -46952,7 +47472,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Масло в шарниры (Живица); Смазка (Сердце горы)</t>
+          <t xml:space="preserve">Масло в шарниры (Живица); Смазка (Сердце горы); Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -46989,7 +47509,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Спуск.b3e6.act; Спуск.b3e6.ctrl</t>
+          <t xml:space="preserve">Спуск.b3e6.act; Спуск.b3e6.ctrl; Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -47026,7 +47546,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шаг механизма (Гнев недр); Спуск.b3b1.ult · ульта; Спуск.b3b1.pas</t>
+          <t xml:space="preserve">Шаг механизма (Гнев недр); Спуск.b3b1.ult · ульта; Спуск.b3b1.pas; Зеркало воли · черта</t>
         </is>
       </c>
     </row>
@@ -47063,7 +47583,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Прочтено: обвал (Тяжёлый обвал); Спуск.b3g1.act; Прочтено: оковы (Паралич); Прочтено: погребение (Погребение) · ульта</t>
+          <t xml:space="preserve">Прочтено: обвал (Тяжёлый обвал); Спуск.b3g1.act; Прочтено: оковы (Паралич); Прочтено: погребение (Погребение) · ульта; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -47322,7 +47842,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тяжкий молот (Гнев недр); В одну отметку (Паралич)</t>
+          <t xml:space="preserve">Тяжкий молот (Гнев недр); В одну отметку (Паралич); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -47359,7 +47879,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цепная серия (Гнев недр); Ржавое звено (Яд)</t>
+          <t xml:space="preserve">Цепная серия (Гнев недр); Ржавое звено (Яд); Срыв покрова · черта</t>
         </is>
       </c>
     </row>
@@ -47396,7 +47916,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Напор (Каменный осколок); Толстая шкура (Скала)</t>
+          <t xml:space="preserve">Напор (Каменный осколок); Толстая шкура (Скала); Дублёная шкура · черта</t>
         </is>
       </c>
     </row>
@@ -47433,7 +47953,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разлив лавы (Огненный вал); Жар жёлоба (Горение)</t>
+          <t xml:space="preserve">Разлив лавы (Огненный вал); Жар жёлоба (Горение); Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -47470,7 +47990,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Янтарный жар (Тёплое дыхание); Оберег (Завеса пламени)</t>
+          <t xml:space="preserve">Янтарный жар (Тёплое дыхание); Оберег (Завеса пламени); Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -47507,7 +48027,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Травление (Клеймо пепла); Спуск.b4e6.act</t>
+          <t xml:space="preserve">Травление (Клеймо пепла); Спуск.b4e6.act; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -47544,7 +48064,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Указ (Осыпание); Весь квартал (Несокрушимость) · ульта; Спуск.b4b1.pas</t>
+          <t xml:space="preserve">Указ (Осыпание); Весь квартал (Несокрушимость) · ульта; Спуск.b4b1.pas; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -47581,7 +48101,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Спуск.b4g1.act; Тяжесть основания (Тяжёлый обвал); Удар посохом (Гнев недр); Трещина в основании (Землетрясение) · ульта</t>
+          <t xml:space="preserve">Спуск.b4g1.act; Тяжесть основания (Тяжёлый обвал); Удар посохом (Гнев недр); Трещина в основании (Землетрясение) · ульта; Зеркало воли · черта</t>
         </is>
       </c>
     </row>
@@ -47840,7 +48360,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поднятое знамя (Пламя сердец); Древко (Искра)</t>
+          <t xml:space="preserve">Поднятое знамя (Пламя сердец); Древко (Искра); Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -47877,7 +48397,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Серпы на осях (Секущий шквал); Просека (Лезвия ветра)</t>
+          <t xml:space="preserve">Серпы на осях (Секущий шквал); Просека (Лезвия ветра); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -47914,7 +48434,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ночные звёзды (Возврат); Верхняя ступень (Круг возвращения)</t>
+          <t xml:space="preserve">Ночные звёзды (Возврат); Верхняя ступень (Круг возвращения); Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -47951,7 +48471,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удар заранее (Обрыв нити); Прочитанный шаг (Остановка)</t>
+          <t xml:space="preserve">Удар заранее (Обрыв нити); Прочитанный шаг (Остановка); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -47988,7 +48508,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лев со знамени (Погребальный костёр); Бронзовая грива (Поджог); Крылья над строем (Испепеление) · ульта</t>
+          <t xml:space="preserve">Лев со знамени (Погребальный костёр); Бронзовая грива (Поджог); Крылья над строем (Испепеление) · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -48025,7 +48545,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Синяя волна (Волна); Холод ночи (Стылый туман); Ночь темнее синего (Великая волна) · ульта</t>
+          <t xml:space="preserve">Синяя волна (Волна); Холод ночи (Стылый туман); Ночь темнее синего (Великая волна) · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48582,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Посох с семью звёздами (Каменный осколок); Небо сказало (Сила гор); Царский приказ (Несокрушимость) · ульта</t>
+          <t xml:space="preserve">Посох с семью звёздами (Каменный осколок); Небо сказало (Сила гор); Царский приказ (Несокрушимость) · ульта; Дублёная шкура · черта</t>
         </is>
       </c>
     </row>
@@ -48099,7 +48619,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Люди.act1; Эхо.Люди.act2; Эхо.Люди.pas; Эхо.Люди.ult1 · ульта; Эхо.Люди.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Люди.act1; Эхо.Люди.act2; Эхо.Люди.pas; Эхо.Люди.ult1 · ульта; Эхо.Люди.ult2 · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -48121,7 +48641,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">forgotten</t>
+          <t xml:space="preserve">awakened</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -48136,7 +48656,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -48395,7 +48915,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Камень к камню (Каменный осколок); Стена без раствора (Каменный заслон)</t>
+          <t xml:space="preserve">Камень к камню (Каменный осколок); Стена без раствора (Каменный заслон); Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -48432,7 +48952,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Камень до реки (Искра); Раскалённый камень (Горение)</t>
+          <t xml:space="preserve">Камень до реки (Искра); Раскалённый камень (Горение); Срыв покрова · черта</t>
         </is>
       </c>
     </row>
@@ -48469,7 +48989,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Затянутый узел (Удар маятника); Перехваченное дыхание (Застывание)</t>
+          <t xml:space="preserve">Затянутый узел (Удар маятника); Перехваченное дыхание (Застывание); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -48506,7 +49026,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Топор для верёвок (Гнев недр); Мост, которого нет (Осыпание)</t>
+          <t xml:space="preserve">Топор для верёвок (Гнев недр); Мост, которого нет (Осыпание); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -48543,7 +49063,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подать (Иссякание); Долг с годами (Старение); Все долины на шнуре (Остановленное время) · ульта</t>
+          <t xml:space="preserve">Подать (Иссякание); Долг с годами (Старение); Все долины на шнуре (Остановленное время) · ульта; Зеркало воли · черта</t>
         </is>
       </c>
     </row>
@@ -48580,7 +49100,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Первый шаг вниз (Гнев недр); Обрыв (Тяжёлый обвал); Дорога вниз (Погребение) · ульта</t>
+          <t xml:space="preserve">Первый шаг вниз (Гнев недр); Обрыв (Тяжёлый обвал); Дорога вниз (Погребение) · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -48617,7 +49137,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Золотой шнур (Огненный вал); Главный шнур (Дымная завеса); Солнце над уступами (Великий пожар) · ульта</t>
+          <t xml:space="preserve">Золотой шнур (Огненный вал); Главный шнур (Дымная завеса); Солнце над уступами (Великий пожар) · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -48654,7 +49174,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Дворфы.act1; Эхо.Дворфы.act2; Эхо.Дворфы.react; Эхо.Дворфы.ult1 · ульта; Эхо.Дворфы.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Дворфы.act1; Эхо.Дворфы.act2; Эхо.Дворфы.react; Эхо.Дворфы.ult1 · ульта; Эхо.Дворфы.ult2 · ульта; Зеркало воли · черта</t>
         </is>
       </c>
     </row>
@@ -48676,7 +49196,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">forgotten</t>
+          <t xml:space="preserve">awakened</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -48691,7 +49211,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -48950,7 +49470,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Прыжок ягуара (Погребальный костёр); Метка когтя (Клеймо пепла)</t>
+          <t xml:space="preserve">Прыжок ягуара (Погребальный костёр); Метка когтя (Клеймо пепла); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -48987,7 +49507,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перо кецаля (Порезы); Стрела, что находит цель (Кровавый смерч)</t>
+          <t xml:space="preserve">Перо кецаля (Порезы); Стрела, что находит цель (Кровавый смерч); Срыв покрова · черта</t>
         </is>
       </c>
     </row>
@@ -49024,7 +49544,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нефритовый дождь (Ледяной дождь); Вычтенный час (Озноб)</t>
+          <t xml:space="preserve">Нефритовый дождь (Ледяной дождь); Вычтенный час (Озноб); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -49061,7 +49581,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чужой день (Застывание); Поворот колеса дней (Иссякание)</t>
+          <t xml:space="preserve">Чужой день (Застывание); Поворот колеса дней (Иссякание); Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -49098,7 +49618,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удар владыки (Гнев недр); Клич ягуаров (Сила гор); Прыжок чёрного ягуара (Погребение) · ульта</t>
+          <t xml:space="preserve">Удар владыки (Гнев недр); Клич ягуаров (Сила гор); Прыжок чёрного ягуара (Погребение) · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -49135,7 +49655,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Счёт дней (Удар маятника); Ветхость дней (Ветхость); Круг дат (Безвременье) · ульта</t>
+          <t xml:space="preserve">Счёт дней (Удар маятника); Ветхость дней (Ветхость); Круг дат (Безвременье) · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -49172,7 +49692,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">По ступеням, как по дням (Прилив); Нефритовый источник (Источник); Все ступени разом (Полноводье) · ульта</t>
+          <t xml:space="preserve">По ступеням, как по дням (Прилив); Нефритовый источник (Источник); Все ступени разом (Полноводье) · ульта; Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -49209,7 +49729,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Эльфы.act; Эхо.Эльфы.pas; Эхо.Эльфы.react; Эхо.Эльфы.ult1 · ульта; Эхо.Эльфы.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Эльфы.act; Эхо.Эльфы.pas; Эхо.Эльфы.react; Эхо.Эльфы.ult1 · ульта; Эхо.Эльфы.ult2 · ульта; Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -49231,7 +49751,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">forgotten</t>
+          <t xml:space="preserve">awakened</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -49246,7 +49766,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -49505,7 +50025,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Туда, где слабее (Погребальный костёр); Вой стае (Боевой жар)</t>
+          <t xml:space="preserve">Туда, где слабее (Погребальный костёр); Вой стае (Боевой жар); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -49542,7 +50062,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Золотые бивни (Каменный осколок); Бляхи с грифонами (Каменная стена)</t>
+          <t xml:space="preserve">Золотые бивни (Каменный осколок); Бляхи с грифонами (Каменная стена); Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -49579,7 +50099,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ветер с неба (Росчерк); Крылья в золотой чешуе (Смерч)</t>
+          <t xml:space="preserve">Ветер с неба (Росчерк); Крылья в золотой чешуе (Смерч); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -49616,7 +50136,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Колокольцы перегона (Отмотка); Зов стада (Возврат)</t>
+          <t xml:space="preserve">Колокольцы перегона (Отмотка); Зов стада (Возврат); Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -49653,7 +50173,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бляха размером со щит (Гнев недр); Сотня за вождём (Раскол); Под копыта сотни (Погребение) · ульта</t>
+          <t xml:space="preserve">Бляха размером со щит (Гнев недр); Сотня за вождём (Раскол); Под копыта сотни (Погребение) · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -49690,7 +50210,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Огонь над курганом (Огненный вал); Золотые когти (Поджог); Падение с неба (Испепеление) · ульта</t>
+          <t xml:space="preserve">Огонь над курганом (Огненный вал); Золотые когти (Поджог); Падение с неба (Испепеление) · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -49727,7 +50247,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Звон бубенцов (Застывание); Сбитый шаг (Утекающий песок); Перегон встал (Остановленное время) · ульта</t>
+          <t xml:space="preserve">Звон бубенцов (Застывание); Сбитый шаг (Утекающий песок); Перегон встал (Остановленное время) · ульта; Зеркало воли · черта</t>
         </is>
       </c>
     </row>
@@ -49764,7 +50284,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Звери.act1; Эхо.Звери.act2; Эхо.Звери.react; Эхо.Звери.ult1 · ульта; Эхо.Звери.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Звери.act1; Эхо.Звери.act2; Эхо.Звери.react; Эхо.Звери.ult1 · ульта; Эхо.Звери.ult2 · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -49786,7 +50306,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">forgotten</t>
+          <t xml:space="preserve">awakened</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -49801,7 +50321,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -50060,7 +50580,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Низкий полёт (Огненный вал); Перья из пламени (Пал)</t>
+          <t xml:space="preserve">Низкий полёт (Огненный вал); Перья из пламени (Пал); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -50097,7 +50617,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удар диском (Погребальный костёр); Крылья-диски (Пепельная метка)</t>
+          <t xml:space="preserve">Удар диском (Погребальный костёр); Крылья-диски (Пепельная метка); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -50134,7 +50654,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Между зеркал (Застывание); Потерянный (Истечение)</t>
+          <t xml:space="preserve">Между зеркал (Застывание); Потерянный (Истечение); Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -50171,7 +50691,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Остывающий уголь (Каменный осколок); Чёрная корка (Гранитная кожа)</t>
+          <t xml:space="preserve">Остывающий уголь (Каменный осколок); Чёрная корка (Гранитная кожа); Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -50208,7 +50728,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Солнца в зеркалах (Удар маятника); Отражение медленнее (Иссякание); Все зеркала разом (Разрыв мгновения) · ульта</t>
+          <t xml:space="preserve">Солнца в зеркалах (Удар маятника); Отражение медленнее (Иссякание); Все зеркала разом (Разрыв мгновения) · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -50245,7 +50765,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Клин змеев (Секущий шквал); Белые перья (Вольный ветер); Клин над равниной (Шторм лезвий) · ульта</t>
+          <t xml:space="preserve">Клин змеев (Секущий шквал); Белые перья (Вольный ветер); Клин над равниной (Шторм лезвий) · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -50282,7 +50802,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Свет для свиты (Живое пламя); Копоть свиты (Завеса пламени); Новое солнце восходит (Негасимый очаг) · ульта</t>
+          <t xml:space="preserve">Свет для свиты (Живое пламя); Копоть свиты (Завеса пламени); Новое солнце восходит (Негасимый очаг) · ульта; Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -50319,7 +50839,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Саганы.act; Эхо.Саганы.pas; Эхо.Саганы.react; Эхо.Саганы.ult1 · ульта; Эхо.Саганы.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Саганы.act; Эхо.Саганы.pas; Эхо.Саганы.react; Эхо.Саганы.ult1 · ульта; Эхо.Саганы.ult2 · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -50341,7 +50861,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">forgotten</t>
+          <t xml:space="preserve">awakened</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -50356,7 +50876,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -50615,7 +51135,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Огненное дыхание (Поджог); Топот (Погребальный костёр)</t>
+          <t xml:space="preserve">Огненное дыхание (Поджог); Топот (Погребальный костёр); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -50652,7 +51172,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обход берега (Каменный осколок); Никого не пропустит (Паралич)</t>
+          <t xml:space="preserve">Обход берега (Каменный осколок); Никого не пропустит (Паралич); Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -50689,7 +51209,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Снова у входа (Застывание); План в медной голове (Иссякание)</t>
+          <t xml:space="preserve">Снова у входа (Застывание); План в медной голове (Иссякание); Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -50726,7 +51246,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лезвия вместо пальцев (Лезвия ветра); Кружение (Секущий шквал)</t>
+          <t xml:space="preserve">Лезвия вместо пальцев (Лезвия ветра); Кружение (Секущий шквал); Срыв покрова · черта</t>
         </is>
       </c>
     </row>
@@ -50763,7 +51283,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медная ладонь (Раскол); Листовая медь (Каменный заслон); Шаг великана (Окаменение) · ульта</t>
+          <t xml:space="preserve">Медная ладонь (Раскол); Листовая медь (Каменный заслон); Шаг великана (Окаменение) · ульта; Дублёная шкура · черта</t>
         </is>
       </c>
     </row>
@@ -50800,7 +51320,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дыхание горна (Огненный вал); Плавленая медь (Горение); Горн открыт (Великий пожар) · ульта</t>
+          <t xml:space="preserve">Дыхание горна (Огненный вал); Плавленая медь (Горение); Горн открыт (Великий пожар) · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -50837,7 +51357,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Починка (Отмотка); Стены лабиринта (Щит мгновения); Как было (Поворот песка) · ульта</t>
+          <t xml:space="preserve">Починка (Отмотка); Стены лабиринта (Щит мгновения); Как было (Поворот песка) · ульта; Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -50874,7 +51394,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Аппараты.act; Эхо.Аппараты.pas1; Эхо.Аппараты.pas2; Эхо.Аппараты.ult1 · ульта; Эхо.Аппараты.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Аппараты.act; Эхо.Аппараты.pas1; Эхо.Аппараты.pas2; Эхо.Аппараты.ult1 · ульта; Эхо.Аппараты.ult2 · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -50896,7 +51416,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">forgotten</t>
+          <t xml:space="preserve">awakened</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -50911,7 +51431,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -51170,7 +51690,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ворота держатся (Каменный заслон); Взгляд бородатого лица (Оцепенение)</t>
+          <t xml:space="preserve">Ворота держатся (Каменный заслон); Взгляд бородатого лица (Оцепенение); Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -51207,7 +51727,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Колдует первое лицо (Песчаная буря); Второе лицо видит (Остановка)</t>
+          <t xml:space="preserve">Колдует первое лицо (Песчаная буря); Второе лицо видит (Остановка); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -51244,7 +51764,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Львиная голова (Погребальный костёр); Змеиная голова (Поджог)</t>
+          <t xml:space="preserve">Львиная голова (Погребальный костёр); Змеиная голова (Поджог); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -51281,7 +51801,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Смена маски (Пыльный вихрь); Чужой облик (Вихревой сброс)</t>
+          <t xml:space="preserve">Смена маски (Пыльный вихрь); Чужой облик (Вихревой сброс); Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -51318,7 +51838,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Маска за маской (Удар маятника); Без лица (Утекающий песок); Седьмая маска (Тлен веков) · ульта</t>
+          <t xml:space="preserve">Маска за маской (Удар маятника); Без лица (Утекающий песок); Седьмая маска (Тлен веков) · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -51355,7 +51875,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шесть крыльев (Каменный осколок); Семь ворот (Каменная стена); Три лица на страже (Каменная крепость) · ульта</t>
+          <t xml:space="preserve">Шесть крыльев (Каменный осколок); Семь ворот (Каменная стена); Три лица на страже (Каменная крепость) · ульта; Дублёная шкура · черта</t>
         </is>
       </c>
     </row>
@@ -51392,7 +51912,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чешуя и крылья (Разлив); Свои меняются (Омовение); Новое тело всем (Талая вода) · ульта</t>
+          <t xml:space="preserve">Чешуя и крылья (Разлив); Свои меняются (Омовение); Новое тело всем (Талая вода) · ульта; Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51949,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Искажённые.act1; Эхо.Искажённые.act2; Эхо.Искажённые.react; Эхо.Искажённые.ult1 · ульта; Эхо.Искажённые.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Искажённые.act1; Эхо.Искажённые.act2; Эхо.Искажённые.react; Эхо.Искажённые.ult1 · ульта; Эхо.Искажённые.ult2 · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -51451,7 +51971,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">forgotten</t>
+          <t xml:space="preserve">awakened</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -51466,7 +51986,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -51725,7 +52245,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Колёса стучат (Искра); Искры из-под колёс (Поджог)</t>
+          <t xml:space="preserve">Колёса стучат (Искра); Искры из-под колёс (Поджог); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -51762,7 +52282,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дверь гробницы (Каменный осколок); Взгляд шакала (Паралич)</t>
+          <t xml:space="preserve">Дверь гробницы (Каменный осколок); Взгляд шакала (Паралич); Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -51799,7 +52319,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пелена (Удар маятника); Время под пеленой (Застывание)</t>
+          <t xml:space="preserve">Пелена (Удар маятника); Время под пеленой (Застывание); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -51836,7 +52356,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рой в лицо (Пыльный вихрь); Жуки из рукавов (Лезвия ветра)</t>
+          <t xml:space="preserve">Рой в лицо (Пыльный вихрь); Жуки из рукавов (Лезвия ветра); Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -51873,7 +52393,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Царский жезл (Каменный осколок); Правит и после (Сила гор); Золотая маска (Каменная крепость) · ульта</t>
+          <t xml:space="preserve">Царский жезл (Каменный осколок); Правит и после (Сила гор); Золотая маска (Каменная крепость) · ульта; Дублёная шкура · черта</t>
         </is>
       </c>
     </row>
@@ -51910,7 +52430,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Весы (Водоворот); Соль на чаше (Зимний холод); Чаша перевесила (Великая волна) · ульта</t>
+          <t xml:space="preserve">Весы (Водоворот); Соль на чаше (Зимний холод); Чаша перевесила (Великая волна) · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -51947,7 +52467,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Золотые жуки (Отсрочка); Льняные пелены (Обратное течение); Не устают (Поворот песка) · ульта</t>
+          <t xml:space="preserve">Золотые жуки (Отсрочка); Льняные пелены (Обратное течение); Не устают (Поворот песка) · ульта; Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -51984,7 +52504,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Нежить.act1; Эхо.Нежить.act2; Эхо.Нежить.react; Эхо.Нежить.ult1 · ульта; Эхо.Нежить.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Нежить.act1; Эхо.Нежить.act2; Эхо.Нежить.react; Эхо.Нежить.ult1 · ульта; Эхо.Нежить.ult2 · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -52006,7 +52526,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">forgotten</t>
+          <t xml:space="preserve">awakened</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -52021,7 +52541,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
@@ -52280,7 +52800,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Катится и давит (Тяжёлый обвал); Гладкая, как речной камень (Каменная кожа)</t>
+          <t xml:space="preserve">Катится и давит (Тяжёлый обвал); Гладкая, как речной камень (Каменная кожа); Каменный лоб · черта</t>
         </is>
       </c>
     </row>
@@ -52317,7 +52837,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резец длиной с меч (Погребальный костёр); Гладкий след (Клеймо пепла)</t>
+          <t xml:space="preserve">Резец длиной с меч (Погребальный костёр); Гладкий след (Клеймо пепла); Ответный выпад · черта</t>
         </is>
       </c>
     </row>
@@ -52354,7 +52874,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тень камня (Удар маятника); Уходит с именем (Бег лет)</t>
+          <t xml:space="preserve">Тень камня (Удар маятника); Уходит с именем (Бег лет); Мимо бури · черта</t>
         </is>
       </c>
     </row>
@@ -52391,7 +52911,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пыль чистых камней (Родник); Пустой круг (Ледяная стена)</t>
+          <t xml:space="preserve">Пыль чистых камней (Родник); Пустой круг (Ледяная стена); Глухая оборона · черта</t>
         </is>
       </c>
     </row>
@@ -52428,7 +52948,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Первое имя (Гнев недр); Резец в руке (Осыпание); Срезано (Погребение) · ульта</t>
+          <t xml:space="preserve">Первое имя (Гнев недр); Резец в руке (Осыпание); Срезано (Погребение) · ульта; Ярость скованного · черта</t>
         </is>
       </c>
     </row>
@@ -52465,7 +52985,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Девять камней (Каменный осколок); Один круг (Каменный заслон); Девять стали одним (Окаменение) · ульта</t>
+          <t xml:space="preserve">Девять камней (Каменный осколок); Один круг (Каменный заслон); Девять стали одним (Окаменение) · ульта; Дублёная шкура · черта</t>
         </is>
       </c>
     </row>
@@ -52502,7 +53022,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зов без слов (Песчаная буря); От круга к кругу (Спешка); Все за ней (Безвременье) · ульта</t>
+          <t xml:space="preserve">Зов без слов (Песчаная буря); От круга к кругу (Спешка); Все за ней (Безвременье) · ульта; Сбить пламя · черта</t>
         </is>
       </c>
     </row>
@@ -52539,7 +53059,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Забытые.act1; Эхо.Забытые.act2; Эхо.Забытые.pas; Эхо.Забытые.ult1 · ульта; Эхо.Забытые.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Забытые.act1; Эхо.Забытые.act2; Эхо.Забытые.pas; Эхо.Забытые.ult1 · ульта; Эхо.Забытые.ult2 · ульта; Зеркало воли · черта</t>
         </is>
       </c>
     </row>
@@ -52561,7 +53081,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">forgotten</t>
+          <t xml:space="preserve">awakened</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -52576,7 +53096,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта; Стряхнуть порчу · черта</t>
         </is>
       </c>
     </row>
